--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D160B71-A20C-48C5-98A1-233FB11BADA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC5F2CE6-DBB3-4AF5-8155-C3F9E189480C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="52">
   <si>
     <t>Aluno</t>
   </si>
@@ -279,147 +279,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1396,7 +1256,9 @@
       <c r="BH3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI3" s="3"/>
+      <c r="BI3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ3" s="3"/>
       <c r="BK3" s="3"/>
       <c r="BL3" s="3"/>
@@ -1643,7 +1505,9 @@
       <c r="BH4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI4" s="3"/>
+      <c r="BI4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ4" s="3"/>
       <c r="BK4" s="3"/>
       <c r="BL4" s="3"/>
@@ -1890,7 +1754,9 @@
       <c r="BH5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI5" s="3"/>
+      <c r="BI5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ5" s="3"/>
       <c r="BK5" s="3"/>
       <c r="BL5" s="3"/>
@@ -2137,7 +2003,9 @@
       <c r="BH6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI6" s="3"/>
+      <c r="BI6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ6" s="3"/>
       <c r="BK6" s="3"/>
       <c r="BL6" s="3"/>
@@ -2384,7 +2252,9 @@
       <c r="BH7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI7" s="3"/>
+      <c r="BI7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ7" s="3"/>
       <c r="BK7" s="3"/>
       <c r="BL7" s="3"/>
@@ -2631,7 +2501,9 @@
       <c r="BH8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BI8" s="3"/>
+      <c r="BI8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ8" s="3"/>
       <c r="BK8" s="3"/>
       <c r="BL8" s="3"/>
@@ -2878,7 +2750,9 @@
       <c r="BH9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI9" s="3"/>
+      <c r="BI9" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BJ9" s="3"/>
       <c r="BK9" s="3"/>
       <c r="BL9" s="3"/>
@@ -3125,7 +2999,9 @@
       <c r="BH10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BI10" s="3"/>
+      <c r="BI10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ10" s="3"/>
       <c r="BK10" s="3"/>
       <c r="BL10" s="3"/>
@@ -3363,7 +3239,9 @@
       <c r="BH11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BI11" s="3"/>
+      <c r="BI11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ11" s="3"/>
       <c r="BK11" s="3"/>
       <c r="BL11" s="3"/>
@@ -3610,7 +3488,9 @@
       <c r="BH12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BI12" s="3"/>
+      <c r="BI12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ12" s="3"/>
       <c r="BK12" s="3"/>
       <c r="BL12" s="3"/>
@@ -3857,7 +3737,9 @@
       <c r="BH13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI13" s="3"/>
+      <c r="BI13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ13" s="3"/>
       <c r="BK13" s="3"/>
       <c r="BL13" s="3"/>
@@ -4104,7 +3986,9 @@
       <c r="BH14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI14" s="3"/>
+      <c r="BI14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ14" s="3"/>
       <c r="BK14" s="3"/>
       <c r="BL14" s="3"/>
@@ -4351,7 +4235,9 @@
       <c r="BH15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI15" s="3"/>
+      <c r="BI15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ15" s="3"/>
       <c r="BK15" s="3"/>
       <c r="BL15" s="3"/>
@@ -4598,7 +4484,9 @@
       <c r="BH16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI16" s="3"/>
+      <c r="BI16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ16" s="3"/>
       <c r="BK16" s="3"/>
       <c r="BL16" s="3"/>
@@ -4824,7 +4712,9 @@
       <c r="BH17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI17" s="3"/>
+      <c r="BI17" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BJ17" s="3"/>
       <c r="BK17" s="3"/>
       <c r="BL17" s="3"/>
@@ -5071,7 +4961,9 @@
       <c r="BH18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI18" s="3"/>
+      <c r="BI18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ18" s="3"/>
       <c r="BK18" s="3"/>
       <c r="BL18" s="3"/>
@@ -5318,7 +5210,9 @@
       <c r="BH19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI19" s="3"/>
+      <c r="BI19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ19" s="3"/>
       <c r="BK19" s="3"/>
       <c r="BL19" s="3"/>
@@ -5544,7 +5438,9 @@
       <c r="BH20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI20" s="3"/>
+      <c r="BI20" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BJ20" s="3"/>
       <c r="BK20" s="3"/>
       <c r="BL20" s="3"/>
@@ -5791,7 +5687,9 @@
       <c r="BH21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BI21" s="3"/>
+      <c r="BI21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ21" s="3"/>
       <c r="BK21" s="3"/>
       <c r="BL21" s="3"/>
@@ -6038,7 +5936,9 @@
       <c r="BH22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI22" s="3"/>
+      <c r="BI22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ22" s="3"/>
       <c r="BK22" s="3"/>
       <c r="BL22" s="3"/>
@@ -6285,7 +6185,9 @@
       <c r="BH23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI23" s="3"/>
+      <c r="BI23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ23" s="3"/>
       <c r="BK23" s="3"/>
       <c r="BL23" s="3"/>
@@ -6532,7 +6434,9 @@
       <c r="BH24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI24" s="3"/>
+      <c r="BI24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ24" s="3"/>
       <c r="BK24" s="3"/>
       <c r="BL24" s="3"/>
@@ -6779,7 +6683,9 @@
       <c r="BH25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI25" s="3"/>
+      <c r="BI25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ25" s="3"/>
       <c r="BK25" s="3"/>
       <c r="BL25" s="3"/>
@@ -7026,7 +6932,9 @@
       <c r="BH26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BI26" s="3"/>
+      <c r="BI26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ26" s="3"/>
       <c r="BK26" s="3"/>
       <c r="BL26" s="3"/>
@@ -7273,7 +7181,9 @@
       <c r="BH27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI27" s="3"/>
+      <c r="BI27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ27" s="3"/>
       <c r="BK27" s="3"/>
       <c r="BL27" s="3"/>
@@ -7520,7 +7430,9 @@
       <c r="BH28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI28" s="3"/>
+      <c r="BI28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ28" s="3"/>
       <c r="BK28" s="3"/>
       <c r="BL28" s="3"/>
@@ -7758,7 +7670,9 @@
       <c r="BH29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BI29" s="3"/>
+      <c r="BI29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ29" s="3"/>
       <c r="BK29" s="3"/>
       <c r="BL29" s="3"/>
@@ -8005,7 +7919,9 @@
       <c r="BH30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI30" s="3"/>
+      <c r="BI30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ30" s="3"/>
       <c r="BK30" s="3"/>
       <c r="BL30" s="3"/>
@@ -8252,7 +8168,9 @@
       <c r="BH31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI31" s="3"/>
+      <c r="BI31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ31" s="3"/>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
@@ -8437,7 +8355,9 @@
       <c r="BH32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI32" s="3"/>
+      <c r="BI32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ32" s="3"/>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.25">
@@ -8622,7 +8542,9 @@
       <c r="BH33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI33" s="3"/>
+      <c r="BI33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ33" s="3"/>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.25">
@@ -8807,7 +8729,9 @@
       <c r="BH34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BI34" s="3"/>
+      <c r="BI34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BJ34" s="3"/>
     </row>
   </sheetData>
@@ -8816,38 +8740,33 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BH4:DH30 BG4:BG34">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BG4:BG34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BJ4:DH30 BI4:BI34">
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BH8">
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BH8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH3:BH34">

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC5F2CE6-DBB3-4AF5-8155-C3F9E189480C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229DF955-1E70-4201-8696-5E49D8BF6E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="53">
   <si>
     <t>Aluno</t>
   </si>
@@ -195,6 +195,9 @@
   <si>
     <t>5P|F</t>
   </si>
+  <si>
+    <t>P | 5F</t>
+  </si>
 </sst>
 </file>
 
@@ -279,7 +282,87 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -827,7 +910,9 @@
       <c r="BH1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BI1" s="1"/>
+      <c r="BI1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1041,7 +1126,9 @@
       <c r="BH2" s="1">
         <v>46275</v>
       </c>
-      <c r="BI2" s="1"/>
+      <c r="BI2" s="1">
+        <v>46280</v>
+      </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -4713,7 +4800,7 @@
         <v>31</v>
       </c>
       <c r="BI17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BJ17" s="3"/>
       <c r="BK17" s="3"/>
@@ -5439,7 +5526,7 @@
         <v>31</v>
       </c>
       <c r="BI20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BJ20" s="3"/>
       <c r="BK20" s="3"/>
@@ -7920,7 +8007,7 @@
         <v>31</v>
       </c>
       <c r="BI30" s="3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="BJ30" s="3"/>
       <c r="BK30" s="3"/>
@@ -8740,38 +8827,43 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BG4:BG34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BJ4:DH30 BI4:BI34">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33">
+    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH3:BH34">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BI3:BI34">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BI3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229DF955-1E70-4201-8696-5E49D8BF6E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D083D49A-A9E0-424B-A43D-0202E51B21E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="53">
   <si>
     <t>Aluno</t>
   </si>
@@ -282,87 +282,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -913,7 +833,9 @@
       <c r="BI1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="BJ1" s="1"/>
+      <c r="BJ1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
       <c r="BM1" s="1"/>
@@ -1129,7 +1051,9 @@
       <c r="BI2" s="1">
         <v>46280</v>
       </c>
-      <c r="BJ2" s="1"/>
+      <c r="BJ2" s="1">
+        <v>46282</v>
+      </c>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
       <c r="BM2" s="1"/>
@@ -1346,7 +1270,9 @@
       <c r="BI3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ3" s="3"/>
+      <c r="BJ3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK3" s="3"/>
       <c r="BL3" s="3"/>
       <c r="BM3" s="3"/>
@@ -1595,7 +1521,9 @@
       <c r="BI4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ4" s="3"/>
+      <c r="BJ4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK4" s="3"/>
       <c r="BL4" s="3"/>
       <c r="BM4" s="3"/>
@@ -1844,7 +1772,9 @@
       <c r="BI5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ5" s="3"/>
+      <c r="BJ5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK5" s="3"/>
       <c r="BL5" s="3"/>
       <c r="BM5" s="3"/>
@@ -2093,7 +2023,9 @@
       <c r="BI6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ6" s="3"/>
+      <c r="BJ6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK6" s="3"/>
       <c r="BL6" s="3"/>
       <c r="BM6" s="3"/>
@@ -2342,7 +2274,9 @@
       <c r="BI7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ7" s="3"/>
+      <c r="BJ7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK7" s="3"/>
       <c r="BL7" s="3"/>
       <c r="BM7" s="3"/>
@@ -2591,7 +2525,9 @@
       <c r="BI8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ8" s="3"/>
+      <c r="BJ8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK8" s="3"/>
       <c r="BL8" s="3"/>
       <c r="BM8" s="3"/>
@@ -2840,7 +2776,9 @@
       <c r="BI9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BJ9" s="3"/>
+      <c r="BJ9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK9" s="3"/>
       <c r="BL9" s="3"/>
       <c r="BM9" s="3"/>
@@ -3089,7 +3027,9 @@
       <c r="BI10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ10" s="3"/>
+      <c r="BJ10" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BK10" s="3"/>
       <c r="BL10" s="3"/>
       <c r="BM10" s="3"/>
@@ -3329,7 +3269,9 @@
       <c r="BI11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ11" s="3"/>
+      <c r="BJ11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK11" s="3"/>
       <c r="BL11" s="3"/>
       <c r="BM11" s="3"/>
@@ -3578,7 +3520,9 @@
       <c r="BI12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ12" s="3"/>
+      <c r="BJ12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK12" s="3"/>
       <c r="BL12" s="3"/>
       <c r="BM12" s="3"/>
@@ -3827,7 +3771,9 @@
       <c r="BI13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ13" s="3"/>
+      <c r="BJ13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK13" s="3"/>
       <c r="BL13" s="3"/>
       <c r="BM13" s="3"/>
@@ -4076,7 +4022,9 @@
       <c r="BI14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ14" s="3"/>
+      <c r="BJ14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK14" s="3"/>
       <c r="BL14" s="3"/>
       <c r="BM14" s="3"/>
@@ -4325,7 +4273,9 @@
       <c r="BI15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ15" s="3"/>
+      <c r="BJ15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK15" s="3"/>
       <c r="BL15" s="3"/>
       <c r="BM15" s="3"/>
@@ -4574,7 +4524,9 @@
       <c r="BI16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ16" s="3"/>
+      <c r="BJ16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK16" s="3"/>
       <c r="BL16" s="3"/>
       <c r="BM16" s="3"/>
@@ -4802,7 +4754,9 @@
       <c r="BI17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ17" s="3"/>
+      <c r="BJ17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK17" s="3"/>
       <c r="BL17" s="3"/>
       <c r="BM17" s="3"/>
@@ -5051,7 +5005,9 @@
       <c r="BI18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ18" s="3"/>
+      <c r="BJ18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK18" s="3"/>
       <c r="BL18" s="3"/>
       <c r="BM18" s="3"/>
@@ -5300,7 +5256,9 @@
       <c r="BI19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ19" s="3"/>
+      <c r="BJ19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK19" s="3"/>
       <c r="BL19" s="3"/>
       <c r="BM19" s="3"/>
@@ -5528,7 +5486,9 @@
       <c r="BI20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ20" s="3"/>
+      <c r="BJ20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK20" s="3"/>
       <c r="BL20" s="3"/>
       <c r="BM20" s="3"/>
@@ -5777,7 +5737,9 @@
       <c r="BI21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ21" s="3"/>
+      <c r="BJ21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK21" s="3"/>
       <c r="BL21" s="3"/>
       <c r="BM21" s="3"/>
@@ -6026,7 +5988,9 @@
       <c r="BI22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ22" s="3"/>
+      <c r="BJ22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK22" s="3"/>
       <c r="BL22" s="3"/>
       <c r="BM22" s="3"/>
@@ -6275,7 +6239,9 @@
       <c r="BI23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ23" s="3"/>
+      <c r="BJ23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK23" s="3"/>
       <c r="BL23" s="3"/>
       <c r="BM23" s="3"/>
@@ -6524,7 +6490,9 @@
       <c r="BI24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ24" s="3"/>
+      <c r="BJ24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK24" s="3"/>
       <c r="BL24" s="3"/>
       <c r="BM24" s="3"/>
@@ -6773,7 +6741,9 @@
       <c r="BI25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ25" s="3"/>
+      <c r="BJ25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK25" s="3"/>
       <c r="BL25" s="3"/>
       <c r="BM25" s="3"/>
@@ -7022,7 +6992,9 @@
       <c r="BI26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ26" s="3"/>
+      <c r="BJ26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK26" s="3"/>
       <c r="BL26" s="3"/>
       <c r="BM26" s="3"/>
@@ -7271,7 +7243,9 @@
       <c r="BI27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ27" s="3"/>
+      <c r="BJ27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK27" s="3"/>
       <c r="BL27" s="3"/>
       <c r="BM27" s="3"/>
@@ -7520,7 +7494,9 @@
       <c r="BI28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ28" s="3"/>
+      <c r="BJ28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK28" s="3"/>
       <c r="BL28" s="3"/>
       <c r="BM28" s="3"/>
@@ -7760,7 +7736,9 @@
       <c r="BI29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ29" s="3"/>
+      <c r="BJ29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK29" s="3"/>
       <c r="BL29" s="3"/>
       <c r="BM29" s="3"/>
@@ -8009,7 +7987,9 @@
       <c r="BI30" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BJ30" s="3"/>
+      <c r="BJ30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BK30" s="3"/>
       <c r="BL30" s="3"/>
       <c r="BM30" s="3"/>
@@ -8258,7 +8238,9 @@
       <c r="BI31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ31" s="3"/>
+      <c r="BJ31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -8445,7 +8427,9 @@
       <c r="BI32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ32" s="3"/>
+      <c r="BJ32" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33">
@@ -8632,7 +8616,9 @@
       <c r="BI33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ33" s="3"/>
+      <c r="BJ33" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34">
@@ -8819,7 +8805,9 @@
       <c r="BI34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BJ34" s="3"/>
+      <c r="BJ34" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N34">
@@ -8827,43 +8815,38 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33">
-    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH3:BH34">
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="F">
+  <conditionalFormatting sqref="BH3:BI34">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BI3:BI34">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BI3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D083D49A-A9E0-424B-A43D-0202E51B21E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEC01C8-3044-45E8-8C9F-ACE8B9944D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,7 +282,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4525,7 +4535,7 @@
         <v>31</v>
       </c>
       <c r="BJ16" s="3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="BK16" s="3"/>
       <c r="BL16" s="3"/>
@@ -8815,38 +8825,43 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33">
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BJ4:DH30">
+    <cfRule type="cellIs" dxfId="5" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB32">
     <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH3:BI34">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BJ16">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BJ16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4SEMESTRE\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEC01C8-3044-45E8-8C9F-ACE8B9944D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D8D339-E115-4834-8956-CECDB9E1113C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="53">
   <si>
     <t>Aluno</t>
   </si>
@@ -846,8 +846,12 @@
       <c r="BJ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BK1" s="1"/>
-      <c r="BL1" s="1"/>
+      <c r="BK1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BM1" s="1"/>
       <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
@@ -1064,8 +1068,12 @@
       <c r="BJ2" s="1">
         <v>46282</v>
       </c>
-      <c r="BK2" s="1"/>
-      <c r="BL2" s="1"/>
+      <c r="BK2" s="1">
+        <v>46287</v>
+      </c>
+      <c r="BL2" s="1">
+        <v>46289</v>
+      </c>
       <c r="BM2" s="1"/>
       <c r="BN2" s="1"/>
       <c r="BO2" s="1"/>
@@ -1283,7 +1291,9 @@
       <c r="BJ3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK3" s="3"/>
+      <c r="BK3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL3" s="3"/>
       <c r="BM3" s="3"/>
       <c r="BN3" s="3"/>
@@ -1534,7 +1544,9 @@
       <c r="BJ4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK4" s="3"/>
+      <c r="BK4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL4" s="3"/>
       <c r="BM4" s="3"/>
       <c r="BN4" s="3"/>
@@ -1785,7 +1797,9 @@
       <c r="BJ5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK5" s="3"/>
+      <c r="BK5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL5" s="3"/>
       <c r="BM5" s="3"/>
       <c r="BN5" s="3"/>
@@ -2036,7 +2050,9 @@
       <c r="BJ6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK6" s="3"/>
+      <c r="BK6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL6" s="3"/>
       <c r="BM6" s="3"/>
       <c r="BN6" s="3"/>
@@ -2287,7 +2303,9 @@
       <c r="BJ7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK7" s="3"/>
+      <c r="BK7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL7" s="3"/>
       <c r="BM7" s="3"/>
       <c r="BN7" s="3"/>
@@ -2538,7 +2556,9 @@
       <c r="BJ8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK8" s="3"/>
+      <c r="BK8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL8" s="3"/>
       <c r="BM8" s="3"/>
       <c r="BN8" s="3"/>
@@ -2789,7 +2809,9 @@
       <c r="BJ9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK9" s="3"/>
+      <c r="BK9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL9" s="3"/>
       <c r="BM9" s="3"/>
       <c r="BN9" s="3"/>
@@ -3040,7 +3062,9 @@
       <c r="BJ10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BK10" s="3"/>
+      <c r="BK10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL10" s="3"/>
       <c r="BM10" s="3"/>
       <c r="BN10" s="3"/>
@@ -3282,7 +3306,9 @@
       <c r="BJ11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK11" s="3"/>
+      <c r="BK11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL11" s="3"/>
       <c r="BM11" s="3"/>
       <c r="BN11" s="3"/>
@@ -3533,7 +3559,9 @@
       <c r="BJ12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK12" s="3"/>
+      <c r="BK12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL12" s="3"/>
       <c r="BM12" s="3"/>
       <c r="BN12" s="3"/>
@@ -3784,7 +3812,9 @@
       <c r="BJ13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK13" s="3"/>
+      <c r="BK13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL13" s="3"/>
       <c r="BM13" s="3"/>
       <c r="BN13" s="3"/>
@@ -4035,7 +4065,9 @@
       <c r="BJ14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK14" s="3"/>
+      <c r="BK14" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BL14" s="3"/>
       <c r="BM14" s="3"/>
       <c r="BN14" s="3"/>
@@ -4286,7 +4318,9 @@
       <c r="BJ15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK15" s="3"/>
+      <c r="BK15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL15" s="3"/>
       <c r="BM15" s="3"/>
       <c r="BN15" s="3"/>
@@ -4537,7 +4571,9 @@
       <c r="BJ16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BK16" s="3"/>
+      <c r="BK16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL16" s="3"/>
       <c r="BM16" s="3"/>
       <c r="BN16" s="3"/>
@@ -4767,7 +4803,9 @@
       <c r="BJ17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK17" s="3"/>
+      <c r="BK17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL17" s="3"/>
       <c r="BM17" s="3"/>
       <c r="BN17" s="3"/>
@@ -5018,7 +5056,9 @@
       <c r="BJ18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK18" s="3"/>
+      <c r="BK18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL18" s="3"/>
       <c r="BM18" s="3"/>
       <c r="BN18" s="3"/>
@@ -5269,7 +5309,9 @@
       <c r="BJ19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK19" s="3"/>
+      <c r="BK19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL19" s="3"/>
       <c r="BM19" s="3"/>
       <c r="BN19" s="3"/>
@@ -5499,7 +5541,9 @@
       <c r="BJ20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK20" s="3"/>
+      <c r="BK20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL20" s="3"/>
       <c r="BM20" s="3"/>
       <c r="BN20" s="3"/>
@@ -5750,7 +5794,9 @@
       <c r="BJ21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK21" s="3"/>
+      <c r="BK21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL21" s="3"/>
       <c r="BM21" s="3"/>
       <c r="BN21" s="3"/>
@@ -6001,7 +6047,9 @@
       <c r="BJ22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK22" s="3"/>
+      <c r="BK22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL22" s="3"/>
       <c r="BM22" s="3"/>
       <c r="BN22" s="3"/>
@@ -6252,7 +6300,9 @@
       <c r="BJ23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK23" s="3"/>
+      <c r="BK23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL23" s="3"/>
       <c r="BM23" s="3"/>
       <c r="BN23" s="3"/>
@@ -6503,7 +6553,9 @@
       <c r="BJ24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK24" s="3"/>
+      <c r="BK24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL24" s="3"/>
       <c r="BM24" s="3"/>
       <c r="BN24" s="3"/>
@@ -6754,7 +6806,9 @@
       <c r="BJ25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK25" s="3"/>
+      <c r="BK25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL25" s="3"/>
       <c r="BM25" s="3"/>
       <c r="BN25" s="3"/>
@@ -7005,7 +7059,9 @@
       <c r="BJ26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK26" s="3"/>
+      <c r="BK26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL26" s="3"/>
       <c r="BM26" s="3"/>
       <c r="BN26" s="3"/>
@@ -7256,7 +7312,9 @@
       <c r="BJ27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK27" s="3"/>
+      <c r="BK27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL27" s="3"/>
       <c r="BM27" s="3"/>
       <c r="BN27" s="3"/>
@@ -7507,7 +7565,9 @@
       <c r="BJ28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK28" s="3"/>
+      <c r="BK28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL28" s="3"/>
       <c r="BM28" s="3"/>
       <c r="BN28" s="3"/>
@@ -7749,7 +7809,9 @@
       <c r="BJ29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK29" s="3"/>
+      <c r="BK29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL29" s="3"/>
       <c r="BM29" s="3"/>
       <c r="BN29" s="3"/>
@@ -8000,7 +8062,9 @@
       <c r="BJ30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BK30" s="3"/>
+      <c r="BK30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BL30" s="3"/>
       <c r="BM30" s="3"/>
       <c r="BN30" s="3"/>
@@ -8251,6 +8315,9 @@
       <c r="BJ31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BK31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -8440,8 +8507,11 @@
       <c r="BJ32" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK32" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8629,8 +8699,11 @@
       <c r="BJ33" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK33" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8816,6 +8889,9 @@
         <v>31</v>
       </c>
       <c r="BJ34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BK34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8834,7 +8910,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BJ4:DH30">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BK31:BK34">
     <cfRule type="cellIs" dxfId="5" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D8D339-E115-4834-8956-CECDB9E1113C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D0F744-3987-4C12-96DC-11E7373FE384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -640,35 +640,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="58" width="7.7109375" customWidth="1"/>
-    <col min="59" max="59" width="8.5703125" customWidth="1"/>
-    <col min="60" max="107" width="7.7109375" customWidth="1"/>
+    <col min="55" max="58" width="7.6640625" customWidth="1"/>
+    <col min="59" max="59" width="8.5546875" customWidth="1"/>
+    <col min="60" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -881,7 +881,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1103,7 +1103,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1356,7 +1356,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1609,7 +1609,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1862,7 +1862,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -2115,7 +2115,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2368,7 +2368,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2621,7 +2621,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2874,7 +2874,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -3127,7 +3127,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3307,7 +3307,7 @@
         <v>31</v>
       </c>
       <c r="BK11" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BL11" s="3"/>
       <c r="BM11" s="3"/>
@@ -3371,7 +3371,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3624,7 +3624,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3877,7 +3877,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -4130,7 +4130,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4383,7 +4383,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4636,7 +4636,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4868,7 +4868,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -5121,7 +5121,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -5374,7 +5374,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5606,7 +5606,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5859,7 +5859,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -6112,7 +6112,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -6365,7 +6365,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6618,7 +6618,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6871,7 +6871,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -7124,7 +7124,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -7377,7 +7377,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7630,7 +7630,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7874,7 +7874,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -8127,7 +8127,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -8319,7 +8319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -8511,7 +8511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8703,7 +8703,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8910,7 +8910,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BK31:BK34">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BK34 H33:I33">
     <cfRule type="cellIs" dxfId="5" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -8948,12 +8948,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8969,7 +8969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8985,7 +8985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -9025,7 +9025,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -9089,7 +9089,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -9209,7 +9209,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -9229,203 +9229,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D0F744-3987-4C12-96DC-11E7373FE384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5866D3A3-F07C-4395-8E01-3CEF721835A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -198,6 +198,12 @@
   <si>
     <t>P | 5F</t>
   </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>saida antecipada</t>
+  </si>
 </sst>
 </file>
 
@@ -282,7 +288,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1295,7 +1321,9 @@
         <v>31</v>
       </c>
       <c r="BL3" s="3"/>
-      <c r="BM3" s="3"/>
+      <c r="BM3" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN3" s="3"/>
       <c r="BO3" s="3"/>
       <c r="BP3" s="3"/>
@@ -1548,7 +1576,9 @@
         <v>31</v>
       </c>
       <c r="BL4" s="3"/>
-      <c r="BM4" s="3"/>
+      <c r="BM4" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN4" s="3"/>
       <c r="BO4" s="3"/>
       <c r="BP4" s="3"/>
@@ -1801,7 +1831,9 @@
         <v>31</v>
       </c>
       <c r="BL5" s="3"/>
-      <c r="BM5" s="3"/>
+      <c r="BM5" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN5" s="3"/>
       <c r="BO5" s="3"/>
       <c r="BP5" s="3"/>
@@ -2054,7 +2086,9 @@
         <v>31</v>
       </c>
       <c r="BL6" s="3"/>
-      <c r="BM6" s="3"/>
+      <c r="BM6" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN6" s="3"/>
       <c r="BO6" s="3"/>
       <c r="BP6" s="3"/>
@@ -2307,7 +2341,9 @@
         <v>31</v>
       </c>
       <c r="BL7" s="3"/>
-      <c r="BM7" s="3"/>
+      <c r="BM7" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN7" s="3"/>
       <c r="BO7" s="3"/>
       <c r="BP7" s="3"/>
@@ -2560,7 +2596,9 @@
         <v>31</v>
       </c>
       <c r="BL8" s="3"/>
-      <c r="BM8" s="3"/>
+      <c r="BM8" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN8" s="3"/>
       <c r="BO8" s="3"/>
       <c r="BP8" s="3"/>
@@ -2813,7 +2851,9 @@
         <v>31</v>
       </c>
       <c r="BL9" s="3"/>
-      <c r="BM9" s="3"/>
+      <c r="BM9" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN9" s="3"/>
       <c r="BO9" s="3"/>
       <c r="BP9" s="3"/>
@@ -3066,7 +3106,9 @@
         <v>31</v>
       </c>
       <c r="BL10" s="3"/>
-      <c r="BM10" s="3"/>
+      <c r="BM10" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN10" s="3"/>
       <c r="BO10" s="3"/>
       <c r="BP10" s="3"/>
@@ -3310,7 +3352,9 @@
         <v>43</v>
       </c>
       <c r="BL11" s="3"/>
-      <c r="BM11" s="3"/>
+      <c r="BM11" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN11" s="3"/>
       <c r="BO11" s="3"/>
       <c r="BP11" s="3"/>
@@ -3563,7 +3607,9 @@
         <v>31</v>
       </c>
       <c r="BL12" s="3"/>
-      <c r="BM12" s="3"/>
+      <c r="BM12" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN12" s="3"/>
       <c r="BO12" s="3"/>
       <c r="BP12" s="3"/>
@@ -3816,7 +3862,9 @@
         <v>31</v>
       </c>
       <c r="BL13" s="3"/>
-      <c r="BM13" s="3"/>
+      <c r="BM13" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN13" s="3"/>
       <c r="BO13" s="3"/>
       <c r="BP13" s="3"/>
@@ -4069,7 +4117,9 @@
         <v>32</v>
       </c>
       <c r="BL14" s="3"/>
-      <c r="BM14" s="3"/>
+      <c r="BM14" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN14" s="3"/>
       <c r="BO14" s="3"/>
       <c r="BP14" s="3"/>
@@ -4322,7 +4372,9 @@
         <v>31</v>
       </c>
       <c r="BL15" s="3"/>
-      <c r="BM15" s="3"/>
+      <c r="BM15" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN15" s="3"/>
       <c r="BO15" s="3"/>
       <c r="BP15" s="3"/>
@@ -4575,7 +4627,9 @@
         <v>31</v>
       </c>
       <c r="BL16" s="3"/>
-      <c r="BM16" s="3"/>
+      <c r="BM16" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN16" s="3"/>
       <c r="BO16" s="3"/>
       <c r="BP16" s="3"/>
@@ -4807,7 +4861,9 @@
         <v>31</v>
       </c>
       <c r="BL17" s="3"/>
-      <c r="BM17" s="3"/>
+      <c r="BM17" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN17" s="3"/>
       <c r="BO17" s="3"/>
       <c r="BP17" s="3"/>
@@ -5060,7 +5116,9 @@
         <v>31</v>
       </c>
       <c r="BL18" s="3"/>
-      <c r="BM18" s="3"/>
+      <c r="BM18" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN18" s="3"/>
       <c r="BO18" s="3"/>
       <c r="BP18" s="3"/>
@@ -5313,7 +5371,9 @@
         <v>31</v>
       </c>
       <c r="BL19" s="3"/>
-      <c r="BM19" s="3"/>
+      <c r="BM19" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN19" s="3"/>
       <c r="BO19" s="3"/>
       <c r="BP19" s="3"/>
@@ -5545,7 +5605,9 @@
         <v>31</v>
       </c>
       <c r="BL20" s="3"/>
-      <c r="BM20" s="3"/>
+      <c r="BM20" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN20" s="3"/>
       <c r="BO20" s="3"/>
       <c r="BP20" s="3"/>
@@ -5798,7 +5860,9 @@
         <v>31</v>
       </c>
       <c r="BL21" s="3"/>
-      <c r="BM21" s="3"/>
+      <c r="BM21" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN21" s="3"/>
       <c r="BO21" s="3"/>
       <c r="BP21" s="3"/>
@@ -6051,7 +6115,9 @@
         <v>31</v>
       </c>
       <c r="BL22" s="3"/>
-      <c r="BM22" s="3"/>
+      <c r="BM22" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN22" s="3"/>
       <c r="BO22" s="3"/>
       <c r="BP22" s="3"/>
@@ -6304,7 +6370,9 @@
         <v>31</v>
       </c>
       <c r="BL23" s="3"/>
-      <c r="BM23" s="3"/>
+      <c r="BM23" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN23" s="3"/>
       <c r="BO23" s="3"/>
       <c r="BP23" s="3"/>
@@ -6557,7 +6625,9 @@
         <v>31</v>
       </c>
       <c r="BL24" s="3"/>
-      <c r="BM24" s="3"/>
+      <c r="BM24" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN24" s="3"/>
       <c r="BO24" s="3"/>
       <c r="BP24" s="3"/>
@@ -6810,7 +6880,9 @@
         <v>31</v>
       </c>
       <c r="BL25" s="3"/>
-      <c r="BM25" s="3"/>
+      <c r="BM25" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN25" s="3"/>
       <c r="BO25" s="3"/>
       <c r="BP25" s="3"/>
@@ -7063,7 +7135,9 @@
         <v>31</v>
       </c>
       <c r="BL26" s="3"/>
-      <c r="BM26" s="3"/>
+      <c r="BM26" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN26" s="3"/>
       <c r="BO26" s="3"/>
       <c r="BP26" s="3"/>
@@ -7316,7 +7390,9 @@
         <v>31</v>
       </c>
       <c r="BL27" s="3"/>
-      <c r="BM27" s="3"/>
+      <c r="BM27" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN27" s="3"/>
       <c r="BO27" s="3"/>
       <c r="BP27" s="3"/>
@@ -7569,7 +7645,9 @@
         <v>31</v>
       </c>
       <c r="BL28" s="3"/>
-      <c r="BM28" s="3"/>
+      <c r="BM28" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="BN28" s="3"/>
       <c r="BO28" s="3"/>
       <c r="BP28" s="3"/>
@@ -7813,7 +7891,9 @@
         <v>31</v>
       </c>
       <c r="BL29" s="3"/>
-      <c r="BM29" s="3"/>
+      <c r="BM29" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN29" s="3"/>
       <c r="BO29" s="3"/>
       <c r="BP29" s="3"/>
@@ -8066,7 +8146,9 @@
         <v>31</v>
       </c>
       <c r="BL30" s="3"/>
-      <c r="BM30" s="3"/>
+      <c r="BM30" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BN30" s="3"/>
       <c r="BO30" s="3"/>
       <c r="BP30" s="3"/>
@@ -8318,6 +8400,9 @@
       <c r="BK31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM31" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -8510,8 +8595,11 @@
       <c r="BK32" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="BM32" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8702,8 +8790,11 @@
       <c r="BK33" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="BM33" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8893,6 +8984,9 @@
       </c>
       <c r="BK34" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="BM34" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -8901,43 +8995,53 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BK34 H33:I33">
-    <cfRule type="cellIs" dxfId="5" priority="12" operator="equal">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BK34 H33:I33 BJ4:DH30 BM33:BM34">
+    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH3:BI34">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ16">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BJ16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BM31">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BM32">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5866D3A3-F07C-4395-8E01-3CEF721835A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B198E-7CC6-46EB-ADEC-2FD75F26E261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -288,7 +288,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -666,35 +676,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="58" width="7.6640625" customWidth="1"/>
-    <col min="59" max="59" width="8.5546875" customWidth="1"/>
-    <col min="60" max="107" width="7.6640625" customWidth="1"/>
+    <col min="55" max="58" width="7.7109375" customWidth="1"/>
+    <col min="59" max="59" width="8.5703125" customWidth="1"/>
+    <col min="60" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -907,7 +917,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1129,7 +1139,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1320,9 +1330,8 @@
       <c r="BK3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL3" s="3"/>
-      <c r="BM3" s="3" t="s">
-        <v>53</v>
+      <c r="BL3" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN3" s="3"/>
       <c r="BO3" s="3"/>
@@ -1384,7 +1393,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1575,9 +1584,8 @@
       <c r="BK4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL4" s="3"/>
-      <c r="BM4" s="3" t="s">
-        <v>54</v>
+      <c r="BL4" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN4" s="3"/>
       <c r="BO4" s="3"/>
@@ -1639,7 +1647,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1830,9 +1838,8 @@
       <c r="BK5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL5" s="3"/>
-      <c r="BM5" s="3" t="s">
-        <v>53</v>
+      <c r="BL5" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN5" s="3"/>
       <c r="BO5" s="3"/>
@@ -1894,7 +1901,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -2085,9 +2092,8 @@
       <c r="BK6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL6" s="3"/>
-      <c r="BM6" s="3" t="s">
-        <v>54</v>
+      <c r="BL6" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN6" s="3"/>
       <c r="BO6" s="3"/>
@@ -2149,7 +2155,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2340,9 +2346,8 @@
       <c r="BK7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL7" s="3"/>
-      <c r="BM7" s="3" t="s">
-        <v>53</v>
+      <c r="BL7" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN7" s="3"/>
       <c r="BO7" s="3"/>
@@ -2404,7 +2409,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2595,9 +2600,8 @@
       <c r="BK8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL8" s="3"/>
-      <c r="BM8" s="3" t="s">
-        <v>53</v>
+      <c r="BL8" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN8" s="3"/>
       <c r="BO8" s="3"/>
@@ -2659,7 +2663,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2850,9 +2854,8 @@
       <c r="BK9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL9" s="3"/>
-      <c r="BM9" s="3" t="s">
-        <v>54</v>
+      <c r="BL9" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN9" s="3"/>
       <c r="BO9" s="3"/>
@@ -2914,7 +2917,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -3105,9 +3108,8 @@
       <c r="BK10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL10" s="3"/>
-      <c r="BM10" s="3" t="s">
-        <v>54</v>
+      <c r="BL10" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN10" s="3"/>
       <c r="BO10" s="3"/>
@@ -3169,7 +3171,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3351,9 +3353,8 @@
       <c r="BK11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BL11" s="3"/>
-      <c r="BM11" s="3" t="s">
-        <v>54</v>
+      <c r="BL11" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN11" s="3"/>
       <c r="BO11" s="3"/>
@@ -3415,7 +3416,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3606,9 +3607,8 @@
       <c r="BK12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL12" s="3"/>
-      <c r="BM12" s="3" t="s">
-        <v>54</v>
+      <c r="BL12" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN12" s="3"/>
       <c r="BO12" s="3"/>
@@ -3670,7 +3670,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3861,9 +3861,8 @@
       <c r="BK13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL13" s="3"/>
-      <c r="BM13" s="3" t="s">
-        <v>54</v>
+      <c r="BL13" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN13" s="3"/>
       <c r="BO13" s="3"/>
@@ -3925,7 +3924,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -4116,9 +4115,8 @@
       <c r="BK14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BL14" s="3"/>
-      <c r="BM14" s="3" t="s">
-        <v>53</v>
+      <c r="BL14" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN14" s="3"/>
       <c r="BO14" s="3"/>
@@ -4180,7 +4178,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4371,9 +4369,8 @@
       <c r="BK15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL15" s="3"/>
-      <c r="BM15" s="3" t="s">
-        <v>54</v>
+      <c r="BL15" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN15" s="3"/>
       <c r="BO15" s="3"/>
@@ -4435,7 +4432,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4626,9 +4623,8 @@
       <c r="BK16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL16" s="3"/>
-      <c r="BM16" s="3" t="s">
-        <v>54</v>
+      <c r="BL16" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN16" s="3"/>
       <c r="BO16" s="3"/>
@@ -4690,7 +4686,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4860,9 +4856,8 @@
       <c r="BK17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL17" s="3"/>
-      <c r="BM17" s="3" t="s">
-        <v>54</v>
+      <c r="BL17" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN17" s="3"/>
       <c r="BO17" s="3"/>
@@ -4924,7 +4919,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -5115,9 +5110,8 @@
       <c r="BK18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL18" s="3"/>
-      <c r="BM18" s="3" t="s">
-        <v>53</v>
+      <c r="BL18" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN18" s="3"/>
       <c r="BO18" s="3"/>
@@ -5179,7 +5173,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -5370,9 +5364,8 @@
       <c r="BK19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL19" s="3"/>
-      <c r="BM19" s="3" t="s">
-        <v>54</v>
+      <c r="BL19" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN19" s="3"/>
       <c r="BO19" s="3"/>
@@ -5434,7 +5427,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5604,9 +5597,8 @@
       <c r="BK20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL20" s="3"/>
-      <c r="BM20" s="3" t="s">
-        <v>54</v>
+      <c r="BL20" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN20" s="3"/>
       <c r="BO20" s="3"/>
@@ -5668,7 +5660,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5859,9 +5851,8 @@
       <c r="BK21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL21" s="3"/>
-      <c r="BM21" s="3" t="s">
-        <v>53</v>
+      <c r="BL21" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN21" s="3"/>
       <c r="BO21" s="3"/>
@@ -5923,7 +5914,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -6114,9 +6105,8 @@
       <c r="BK22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL22" s="3"/>
-      <c r="BM22" s="3" t="s">
-        <v>54</v>
+      <c r="BL22" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN22" s="3"/>
       <c r="BO22" s="3"/>
@@ -6178,7 +6168,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -6369,9 +6359,8 @@
       <c r="BK23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL23" s="3"/>
-      <c r="BM23" s="3" t="s">
-        <v>53</v>
+      <c r="BL23" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN23" s="3"/>
       <c r="BO23" s="3"/>
@@ -6433,7 +6422,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6624,9 +6613,8 @@
       <c r="BK24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL24" s="3"/>
-      <c r="BM24" s="3" t="s">
-        <v>54</v>
+      <c r="BL24" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN24" s="3"/>
       <c r="BO24" s="3"/>
@@ -6688,7 +6676,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6879,9 +6867,8 @@
       <c r="BK25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL25" s="3"/>
-      <c r="BM25" s="3" t="s">
-        <v>54</v>
+      <c r="BL25" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN25" s="3"/>
       <c r="BO25" s="3"/>
@@ -6943,7 +6930,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -7134,9 +7121,8 @@
       <c r="BK26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL26" s="3"/>
-      <c r="BM26" s="3" t="s">
-        <v>53</v>
+      <c r="BL26" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN26" s="3"/>
       <c r="BO26" s="3"/>
@@ -7198,7 +7184,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -7389,9 +7375,8 @@
       <c r="BK27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL27" s="3"/>
-      <c r="BM27" s="3" t="s">
-        <v>54</v>
+      <c r="BL27" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN27" s="3"/>
       <c r="BO27" s="3"/>
@@ -7453,7 +7438,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7644,9 +7629,8 @@
       <c r="BK28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL28" s="3"/>
-      <c r="BM28" s="3" t="s">
-        <v>53</v>
+      <c r="BL28" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN28" s="3"/>
       <c r="BO28" s="3"/>
@@ -7708,7 +7692,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7890,9 +7874,8 @@
       <c r="BK29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL29" s="3"/>
-      <c r="BM29" s="3" t="s">
-        <v>54</v>
+      <c r="BL29" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN29" s="3"/>
       <c r="BO29" s="3"/>
@@ -7954,7 +7937,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -8145,9 +8128,8 @@
       <c r="BK30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BL30" s="3"/>
-      <c r="BM30" s="3" t="s">
-        <v>54</v>
+      <c r="BL30" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BN30" s="3"/>
       <c r="BO30" s="3"/>
@@ -8209,7 +8191,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -8400,11 +8382,11 @@
       <c r="BK31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BM31" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+      <c r="BL31" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -8595,11 +8577,11 @@
       <c r="BK32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BM32" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="BL32" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8790,11 +8772,11 @@
       <c r="BK33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BM33" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="BL33" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8985,8 +8967,8 @@
       <c r="BK34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BM34" s="3" t="s">
-        <v>53</v>
+      <c r="BL34" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -8995,51 +8977,432 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BK34 H33:I33 BJ4:DH30 BM33:BM34">
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
+  <conditionalFormatting sqref="AU3:BA3 BF3:BL3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BL30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BK31:BL34 BN3:DH30">
+    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH3:BI34">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ16">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BJ16)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM31">
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>26132246</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>26132200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>26132302</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>26132277</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>26132197</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>26132286</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>26132281</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>26132340</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>26133020</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>26132271</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>26132244</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>26132204</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>26132220</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>26132184</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>26133029</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>26132288</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>26132330</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>26133024</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>26132248</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>26132180</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>26132269</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>26132202</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>26132265</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>26132252</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>26132242</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26132240</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>26133022</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>26132250</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>26132238</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>26132275</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>26132256</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>26132304</v>
+      </c>
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B33">
+    <sortCondition ref="B1:B33"/>
+  </sortState>
+  <conditionalFormatting sqref="C2:C29">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM32">
+  <conditionalFormatting sqref="C30:C33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9049,487 +9412,206 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>26132246</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>26132200</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>26132302</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>26132277</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>26132197</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>26132286</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>26132281</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>26132340</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>26133020</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>26132271</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>26132244</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>26132204</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>26132220</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>26132184</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>26133029</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>26132288</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>26132330</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>26133024</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>26132248</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>26132180</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>26132269</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>26132202</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>26132265</v>
-      </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>26132252</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>26132242</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>26132240</v>
-      </c>
-      <c r="B27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>26133022</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>26132250</v>
-      </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>26132238</v>
-      </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>26132275</v>
-      </c>
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>26132256</v>
-      </c>
-      <c r="B32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>26132304</v>
-      </c>
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B33">
-    <sortCondition ref="B1:B33"/>
-  </sortState>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B198E-7CC6-46EB-ADEC-2FD75F26E261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4108B1F4-05A5-4F07-A629-5D33709952FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -288,27 +288,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -888,8 +868,12 @@
       <c r="BL1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BM1" s="1"/>
-      <c r="BN1" s="1"/>
+      <c r="BM1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
@@ -1110,8 +1094,12 @@
       <c r="BL2" s="1">
         <v>46289</v>
       </c>
-      <c r="BM2" s="1"/>
-      <c r="BN2" s="1"/>
+      <c r="BM2" s="1">
+        <v>46294</v>
+      </c>
+      <c r="BN2" s="1">
+        <v>46296</v>
+      </c>
       <c r="BO2" s="1"/>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="1"/>
@@ -1332,6 +1320,9 @@
       </c>
       <c r="BL3" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="BN3" s="3"/>
       <c r="BO3" s="3"/>
@@ -1587,6 +1578,9 @@
       <c r="BL4" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN4" s="3"/>
       <c r="BO4" s="3"/>
       <c r="BP4" s="3"/>
@@ -1841,6 +1835,9 @@
       <c r="BL5" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN5" s="3"/>
       <c r="BO5" s="3"/>
       <c r="BP5" s="3"/>
@@ -2095,6 +2092,9 @@
       <c r="BL6" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN6" s="3"/>
       <c r="BO6" s="3"/>
       <c r="BP6" s="3"/>
@@ -2349,6 +2349,9 @@
       <c r="BL7" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN7" s="3"/>
       <c r="BO7" s="3"/>
       <c r="BP7" s="3"/>
@@ -2603,6 +2606,9 @@
       <c r="BL8" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN8" s="3"/>
       <c r="BO8" s="3"/>
       <c r="BP8" s="3"/>
@@ -2857,6 +2863,9 @@
       <c r="BL9" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN9" s="3"/>
       <c r="BO9" s="3"/>
       <c r="BP9" s="3"/>
@@ -3111,6 +3120,9 @@
       <c r="BL10" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN10" s="3"/>
       <c r="BO10" s="3"/>
       <c r="BP10" s="3"/>
@@ -3356,6 +3368,9 @@
       <c r="BL11" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN11" s="3"/>
       <c r="BO11" s="3"/>
       <c r="BP11" s="3"/>
@@ -3610,6 +3625,9 @@
       <c r="BL12" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN12" s="3"/>
       <c r="BO12" s="3"/>
       <c r="BP12" s="3"/>
@@ -3864,6 +3882,9 @@
       <c r="BL13" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN13" s="3"/>
       <c r="BO13" s="3"/>
       <c r="BP13" s="3"/>
@@ -4118,6 +4139,9 @@
       <c r="BL14" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN14" s="3"/>
       <c r="BO14" s="3"/>
       <c r="BP14" s="3"/>
@@ -4372,6 +4396,9 @@
       <c r="BL15" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN15" s="3"/>
       <c r="BO15" s="3"/>
       <c r="BP15" s="3"/>
@@ -4626,6 +4653,9 @@
       <c r="BL16" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN16" s="3"/>
       <c r="BO16" s="3"/>
       <c r="BP16" s="3"/>
@@ -4859,6 +4889,9 @@
       <c r="BL17" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN17" s="3"/>
       <c r="BO17" s="3"/>
       <c r="BP17" s="3"/>
@@ -5113,6 +5146,9 @@
       <c r="BL18" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN18" s="3"/>
       <c r="BO18" s="3"/>
       <c r="BP18" s="3"/>
@@ -5367,6 +5403,9 @@
       <c r="BL19" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN19" s="3"/>
       <c r="BO19" s="3"/>
       <c r="BP19" s="3"/>
@@ -5600,6 +5639,9 @@
       <c r="BL20" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN20" s="3"/>
       <c r="BO20" s="3"/>
       <c r="BP20" s="3"/>
@@ -5854,6 +5896,9 @@
       <c r="BL21" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN21" s="3"/>
       <c r="BO21" s="3"/>
       <c r="BP21" s="3"/>
@@ -6108,6 +6153,9 @@
       <c r="BL22" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN22" s="3"/>
       <c r="BO22" s="3"/>
       <c r="BP22" s="3"/>
@@ -6362,6 +6410,9 @@
       <c r="BL23" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN23" s="3"/>
       <c r="BO23" s="3"/>
       <c r="BP23" s="3"/>
@@ -6616,6 +6667,9 @@
       <c r="BL24" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN24" s="3"/>
       <c r="BO24" s="3"/>
       <c r="BP24" s="3"/>
@@ -6870,6 +6924,9 @@
       <c r="BL25" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN25" s="3"/>
       <c r="BO25" s="3"/>
       <c r="BP25" s="3"/>
@@ -7124,6 +7181,9 @@
       <c r="BL26" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN26" s="3"/>
       <c r="BO26" s="3"/>
       <c r="BP26" s="3"/>
@@ -7378,6 +7438,9 @@
       <c r="BL27" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN27" s="3"/>
       <c r="BO27" s="3"/>
       <c r="BP27" s="3"/>
@@ -7632,6 +7695,9 @@
       <c r="BL28" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN28" s="3"/>
       <c r="BO28" s="3"/>
       <c r="BP28" s="3"/>
@@ -7877,6 +7943,9 @@
       <c r="BL29" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN29" s="3"/>
       <c r="BO29" s="3"/>
       <c r="BP29" s="3"/>
@@ -8131,6 +8200,9 @@
       <c r="BL30" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BN30" s="3"/>
       <c r="BO30" s="3"/>
       <c r="BP30" s="3"/>
@@ -8385,6 +8457,9 @@
       <c r="BL31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BM31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -8580,8 +8655,11 @@
       <c r="BL32" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM32" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8775,8 +8853,11 @@
       <c r="BL33" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM33" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8968,6 +9049,9 @@
         <v>31</v>
       </c>
       <c r="BL34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BM34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8977,42 +9061,42 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:BL3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BL30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BK31:BL34 BN3:DH30">
-    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 BN3:DH30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BF3:BM3 BJ4:BM30 BK31:BM34">
+    <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH3:BI34">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ16">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BJ16)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9397,12 +9481,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B33">
     <sortCondition ref="B1:B33"/>
   </sortState>
-  <conditionalFormatting sqref="C2:C29">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C30:C33">
+  <conditionalFormatting sqref="C2:C33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4108B1F4-05A5-4F07-A629-5D33709952FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A70CE8-AB87-4EB2-AA49-9D745A6FC6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -656,35 +656,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="58" width="7.7109375" customWidth="1"/>
-    <col min="59" max="59" width="8.5703125" customWidth="1"/>
-    <col min="60" max="107" width="7.7109375" customWidth="1"/>
+    <col min="55" max="58" width="7.6640625" customWidth="1"/>
+    <col min="59" max="59" width="8.5546875" customWidth="1"/>
+    <col min="60" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -901,7 +901,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1127,7 +1127,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1384,7 +1384,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1641,7 +1641,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1898,7 +1898,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -2155,7 +2155,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2412,7 +2412,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2669,7 +2669,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2926,7 +2926,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -3121,7 +3121,7 @@
         <v>31</v>
       </c>
       <c r="BM10" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BN10" s="3"/>
       <c r="BO10" s="3"/>
@@ -3183,7 +3183,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3369,7 +3369,7 @@
         <v>31</v>
       </c>
       <c r="BM11" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BN11" s="3"/>
       <c r="BO11" s="3"/>
@@ -3431,7 +3431,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3688,7 +3688,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3945,7 +3945,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -4202,7 +4202,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4459,7 +4459,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4716,7 +4716,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4952,7 +4952,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -5209,7 +5209,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -5466,7 +5466,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5702,7 +5702,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5959,7 +5959,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -6216,7 +6216,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -6473,7 +6473,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6730,7 +6730,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6987,7 +6987,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -7244,7 +7244,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -7501,7 +7501,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7758,7 +7758,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -8006,7 +8006,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -8263,7 +8263,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -8458,10 +8458,10 @@
         <v>31</v>
       </c>
       <c r="BM31" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -8659,7 +8659,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8857,7 +8857,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9070,7 +9070,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 BN3:DH30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BF3:BM3 BJ4:BM30 BK31:BM34">
+  <conditionalFormatting sqref="AU3:BA3 BF3:BM3 BC3:BC21 D3:I30 K3:T30 BN3:DH30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33">
     <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9108,13 +9108,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -9136,7 +9136,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -9224,7 +9224,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -9235,7 +9235,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -9268,7 +9268,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -9323,7 +9323,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -9334,7 +9334,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -9400,7 +9400,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -9411,7 +9411,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -9455,7 +9455,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -9494,203 +9494,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A70CE8-AB87-4EB2-AA49-9D745A6FC6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D6ECCD-10CE-4857-8291-2B3B769BA434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -656,35 +656,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="58" width="7.6640625" customWidth="1"/>
-    <col min="59" max="59" width="8.5546875" customWidth="1"/>
-    <col min="60" max="107" width="7.6640625" customWidth="1"/>
+    <col min="55" max="58" width="7.7109375" customWidth="1"/>
+    <col min="59" max="59" width="8.5703125" customWidth="1"/>
+    <col min="60" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -901,7 +901,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1127,7 +1127,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1324,7 +1324,9 @@
       <c r="BM3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BN3" s="3"/>
+      <c r="BN3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO3" s="3"/>
       <c r="BP3" s="3"/>
       <c r="BQ3" s="3"/>
@@ -1384,7 +1386,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1581,7 +1583,9 @@
       <c r="BM4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN4" s="3"/>
+      <c r="BN4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO4" s="3"/>
       <c r="BP4" s="3"/>
       <c r="BQ4" s="3"/>
@@ -1641,7 +1645,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1838,7 +1842,9 @@
       <c r="BM5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN5" s="3"/>
+      <c r="BN5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO5" s="3"/>
       <c r="BP5" s="3"/>
       <c r="BQ5" s="3"/>
@@ -1898,7 +1904,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -2095,7 +2101,9 @@
       <c r="BM6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN6" s="3"/>
+      <c r="BN6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO6" s="3"/>
       <c r="BP6" s="3"/>
       <c r="BQ6" s="3"/>
@@ -2155,7 +2163,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2352,7 +2360,9 @@
       <c r="BM7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN7" s="3"/>
+      <c r="BN7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO7" s="3"/>
       <c r="BP7" s="3"/>
       <c r="BQ7" s="3"/>
@@ -2412,7 +2422,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2609,7 +2619,9 @@
       <c r="BM8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN8" s="3"/>
+      <c r="BN8" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BO8" s="3"/>
       <c r="BP8" s="3"/>
       <c r="BQ8" s="3"/>
@@ -2669,7 +2681,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2866,7 +2878,9 @@
       <c r="BM9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN9" s="3"/>
+      <c r="BN9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO9" s="3"/>
       <c r="BP9" s="3"/>
       <c r="BQ9" s="3"/>
@@ -2926,7 +2940,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -3123,7 +3137,9 @@
       <c r="BM10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BN10" s="3"/>
+      <c r="BN10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO10" s="3"/>
       <c r="BP10" s="3"/>
       <c r="BQ10" s="3"/>
@@ -3183,7 +3199,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3371,7 +3387,9 @@
       <c r="BM11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BN11" s="3"/>
+      <c r="BN11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO11" s="3"/>
       <c r="BP11" s="3"/>
       <c r="BQ11" s="3"/>
@@ -3431,7 +3449,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3628,7 +3646,9 @@
       <c r="BM12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN12" s="3"/>
+      <c r="BN12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO12" s="3"/>
       <c r="BP12" s="3"/>
       <c r="BQ12" s="3"/>
@@ -3688,7 +3708,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3885,7 +3905,9 @@
       <c r="BM13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN13" s="3"/>
+      <c r="BN13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO13" s="3"/>
       <c r="BP13" s="3"/>
       <c r="BQ13" s="3"/>
@@ -3945,7 +3967,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -4142,7 +4164,9 @@
       <c r="BM14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN14" s="3"/>
+      <c r="BN14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO14" s="3"/>
       <c r="BP14" s="3"/>
       <c r="BQ14" s="3"/>
@@ -4202,7 +4226,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4399,7 +4423,9 @@
       <c r="BM15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN15" s="3"/>
+      <c r="BN15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO15" s="3"/>
       <c r="BP15" s="3"/>
       <c r="BQ15" s="3"/>
@@ -4459,7 +4485,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4656,7 +4682,9 @@
       <c r="BM16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN16" s="3"/>
+      <c r="BN16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO16" s="3"/>
       <c r="BP16" s="3"/>
       <c r="BQ16" s="3"/>
@@ -4716,7 +4744,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4892,7 +4920,9 @@
       <c r="BM17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN17" s="3"/>
+      <c r="BN17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO17" s="3"/>
       <c r="BP17" s="3"/>
       <c r="BQ17" s="3"/>
@@ -4952,7 +4982,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -5149,7 +5179,9 @@
       <c r="BM18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN18" s="3"/>
+      <c r="BN18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO18" s="3"/>
       <c r="BP18" s="3"/>
       <c r="BQ18" s="3"/>
@@ -5209,7 +5241,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -5406,7 +5438,9 @@
       <c r="BM19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN19" s="3"/>
+      <c r="BN19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO19" s="3"/>
       <c r="BP19" s="3"/>
       <c r="BQ19" s="3"/>
@@ -5466,7 +5500,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5642,7 +5676,9 @@
       <c r="BM20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN20" s="3"/>
+      <c r="BN20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO20" s="3"/>
       <c r="BP20" s="3"/>
       <c r="BQ20" s="3"/>
@@ -5702,7 +5738,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5899,7 +5935,9 @@
       <c r="BM21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN21" s="3"/>
+      <c r="BN21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO21" s="3"/>
       <c r="BP21" s="3"/>
       <c r="BQ21" s="3"/>
@@ -5959,7 +5997,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -6156,7 +6194,9 @@
       <c r="BM22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN22" s="3"/>
+      <c r="BN22" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BO22" s="3"/>
       <c r="BP22" s="3"/>
       <c r="BQ22" s="3"/>
@@ -6216,7 +6256,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -6413,7 +6453,9 @@
       <c r="BM23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN23" s="3"/>
+      <c r="BN23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO23" s="3"/>
       <c r="BP23" s="3"/>
       <c r="BQ23" s="3"/>
@@ -6473,7 +6515,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6670,7 +6712,9 @@
       <c r="BM24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN24" s="3"/>
+      <c r="BN24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO24" s="3"/>
       <c r="BP24" s="3"/>
       <c r="BQ24" s="3"/>
@@ -6730,7 +6774,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6927,7 +6971,9 @@
       <c r="BM25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN25" s="3"/>
+      <c r="BN25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO25" s="3"/>
       <c r="BP25" s="3"/>
       <c r="BQ25" s="3"/>
@@ -6987,7 +7033,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -7184,7 +7230,9 @@
       <c r="BM26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN26" s="3"/>
+      <c r="BN26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO26" s="3"/>
       <c r="BP26" s="3"/>
       <c r="BQ26" s="3"/>
@@ -7244,7 +7292,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -7441,7 +7489,9 @@
       <c r="BM27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN27" s="3"/>
+      <c r="BN27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO27" s="3"/>
       <c r="BP27" s="3"/>
       <c r="BQ27" s="3"/>
@@ -7501,7 +7551,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7698,7 +7748,9 @@
       <c r="BM28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN28" s="3"/>
+      <c r="BN28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO28" s="3"/>
       <c r="BP28" s="3"/>
       <c r="BQ28" s="3"/>
@@ -7758,7 +7810,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7946,7 +7998,9 @@
       <c r="BM29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN29" s="3"/>
+      <c r="BN29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO29" s="3"/>
       <c r="BP29" s="3"/>
       <c r="BQ29" s="3"/>
@@ -8006,7 +8060,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -8203,7 +8257,9 @@
       <c r="BM30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BN30" s="3"/>
+      <c r="BN30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BO30" s="3"/>
       <c r="BP30" s="3"/>
       <c r="BQ30" s="3"/>
@@ -8263,7 +8319,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -8460,8 +8516,11 @@
       <c r="BM31" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+      <c r="BN31" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -8658,8 +8717,11 @@
       <c r="BM32" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="BN32" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8856,8 +8918,11 @@
       <c r="BM33" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="BN33" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9052,6 +9117,9 @@
         <v>31</v>
       </c>
       <c r="BM34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BN34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9070,7 +9138,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:BM3 BC3:BC21 D3:I30 K3:T30 BN3:DH30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33">
+  <conditionalFormatting sqref="AU3:BA3 BF3:BM3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BN3:DH22 BO23:DH30 BN23:BN34">
     <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9108,13 +9176,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9125,7 +9193,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -9136,7 +9204,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -9147,7 +9215,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -9158,7 +9226,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -9169,7 +9237,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -9180,7 +9248,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -9191,7 +9259,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -9202,7 +9270,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -9213,7 +9281,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -9224,7 +9292,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -9235,7 +9303,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -9246,7 +9314,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -9257,7 +9325,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -9268,7 +9336,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -9279,7 +9347,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -9290,7 +9358,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -9301,7 +9369,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -9312,7 +9380,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -9323,7 +9391,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -9334,7 +9402,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -9345,7 +9413,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -9356,7 +9424,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -9367,7 +9435,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -9378,7 +9446,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -9389,7 +9457,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -9400,7 +9468,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -9411,7 +9479,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -9422,7 +9490,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -9433,7 +9501,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -9444,7 +9512,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -9455,7 +9523,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -9466,7 +9534,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -9494,203 +9562,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D6ECCD-10CE-4857-8291-2B3B769BA434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D9B206-1F32-4E61-98BF-ABAB757F1246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -874,7 +874,9 @@
       <c r="BN1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BO1" s="1"/>
+      <c r="BO1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
@@ -1100,7 +1102,9 @@
       <c r="BN2" s="1">
         <v>46296</v>
       </c>
-      <c r="BO2" s="1"/>
+      <c r="BO2" s="1">
+        <v>46298</v>
+      </c>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="1"/>
       <c r="BR2" s="1"/>
@@ -1327,7 +1331,9 @@
       <c r="BN3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO3" s="3"/>
+      <c r="BO3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP3" s="3"/>
       <c r="BQ3" s="3"/>
       <c r="BR3" s="3"/>
@@ -1586,7 +1592,9 @@
       <c r="BN4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO4" s="3"/>
+      <c r="BO4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP4" s="3"/>
       <c r="BQ4" s="3"/>
       <c r="BR4" s="3"/>
@@ -1845,7 +1853,9 @@
       <c r="BN5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO5" s="3"/>
+      <c r="BO5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP5" s="3"/>
       <c r="BQ5" s="3"/>
       <c r="BR5" s="3"/>
@@ -2104,7 +2114,9 @@
       <c r="BN6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO6" s="3"/>
+      <c r="BO6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP6" s="3"/>
       <c r="BQ6" s="3"/>
       <c r="BR6" s="3"/>
@@ -2363,7 +2375,9 @@
       <c r="BN7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO7" s="3"/>
+      <c r="BO7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP7" s="3"/>
       <c r="BQ7" s="3"/>
       <c r="BR7" s="3"/>
@@ -2622,7 +2636,9 @@
       <c r="BN8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BO8" s="3"/>
+      <c r="BO8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP8" s="3"/>
       <c r="BQ8" s="3"/>
       <c r="BR8" s="3"/>
@@ -2881,7 +2897,9 @@
       <c r="BN9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO9" s="3"/>
+      <c r="BO9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP9" s="3"/>
       <c r="BQ9" s="3"/>
       <c r="BR9" s="3"/>
@@ -3140,7 +3158,9 @@
       <c r="BN10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO10" s="3"/>
+      <c r="BO10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP10" s="3"/>
       <c r="BQ10" s="3"/>
       <c r="BR10" s="3"/>
@@ -3390,7 +3410,9 @@
       <c r="BN11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO11" s="3"/>
+      <c r="BO11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP11" s="3"/>
       <c r="BQ11" s="3"/>
       <c r="BR11" s="3"/>
@@ -3649,7 +3671,9 @@
       <c r="BN12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO12" s="3"/>
+      <c r="BO12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP12" s="3"/>
       <c r="BQ12" s="3"/>
       <c r="BR12" s="3"/>
@@ -3908,7 +3932,9 @@
       <c r="BN13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO13" s="3"/>
+      <c r="BO13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP13" s="3"/>
       <c r="BQ13" s="3"/>
       <c r="BR13" s="3"/>
@@ -4167,7 +4193,9 @@
       <c r="BN14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO14" s="3"/>
+      <c r="BO14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP14" s="3"/>
       <c r="BQ14" s="3"/>
       <c r="BR14" s="3"/>
@@ -4426,7 +4454,9 @@
       <c r="BN15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO15" s="3"/>
+      <c r="BO15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP15" s="3"/>
       <c r="BQ15" s="3"/>
       <c r="BR15" s="3"/>
@@ -4685,7 +4715,9 @@
       <c r="BN16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO16" s="3"/>
+      <c r="BO16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP16" s="3"/>
       <c r="BQ16" s="3"/>
       <c r="BR16" s="3"/>
@@ -4923,7 +4955,9 @@
       <c r="BN17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO17" s="3"/>
+      <c r="BO17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP17" s="3"/>
       <c r="BQ17" s="3"/>
       <c r="BR17" s="3"/>
@@ -5182,7 +5216,9 @@
       <c r="BN18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO18" s="3"/>
+      <c r="BO18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP18" s="3"/>
       <c r="BQ18" s="3"/>
       <c r="BR18" s="3"/>
@@ -5441,7 +5477,9 @@
       <c r="BN19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO19" s="3"/>
+      <c r="BO19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP19" s="3"/>
       <c r="BQ19" s="3"/>
       <c r="BR19" s="3"/>
@@ -5679,7 +5717,9 @@
       <c r="BN20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO20" s="3"/>
+      <c r="BO20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP20" s="3"/>
       <c r="BQ20" s="3"/>
       <c r="BR20" s="3"/>
@@ -5938,7 +5978,9 @@
       <c r="BN21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO21" s="3"/>
+      <c r="BO21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP21" s="3"/>
       <c r="BQ21" s="3"/>
       <c r="BR21" s="3"/>
@@ -6197,7 +6239,9 @@
       <c r="BN22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BO22" s="3"/>
+      <c r="BO22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP22" s="3"/>
       <c r="BQ22" s="3"/>
       <c r="BR22" s="3"/>
@@ -6456,7 +6500,9 @@
       <c r="BN23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO23" s="3"/>
+      <c r="BO23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP23" s="3"/>
       <c r="BQ23" s="3"/>
       <c r="BR23" s="3"/>
@@ -6715,7 +6761,9 @@
       <c r="BN24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO24" s="3"/>
+      <c r="BO24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP24" s="3"/>
       <c r="BQ24" s="3"/>
       <c r="BR24" s="3"/>
@@ -6974,7 +7022,9 @@
       <c r="BN25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO25" s="3"/>
+      <c r="BO25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP25" s="3"/>
       <c r="BQ25" s="3"/>
       <c r="BR25" s="3"/>
@@ -7233,7 +7283,9 @@
       <c r="BN26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO26" s="3"/>
+      <c r="BO26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP26" s="3"/>
       <c r="BQ26" s="3"/>
       <c r="BR26" s="3"/>
@@ -7492,7 +7544,9 @@
       <c r="BN27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO27" s="3"/>
+      <c r="BO27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP27" s="3"/>
       <c r="BQ27" s="3"/>
       <c r="BR27" s="3"/>
@@ -7751,7 +7805,9 @@
       <c r="BN28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO28" s="3"/>
+      <c r="BO28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP28" s="3"/>
       <c r="BQ28" s="3"/>
       <c r="BR28" s="3"/>
@@ -8001,7 +8057,9 @@
       <c r="BN29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO29" s="3"/>
+      <c r="BO29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP29" s="3"/>
       <c r="BQ29" s="3"/>
       <c r="BR29" s="3"/>
@@ -8260,7 +8318,9 @@
       <c r="BN30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BO30" s="3"/>
+      <c r="BO30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BP30" s="3"/>
       <c r="BQ30" s="3"/>
       <c r="BR30" s="3"/>
@@ -8519,6 +8579,9 @@
       <c r="BN31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BO31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -8720,8 +8783,11 @@
       <c r="BN32" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO32" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8921,8 +8987,11 @@
       <c r="BN33" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO33" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9120,6 +9189,9 @@
         <v>31</v>
       </c>
       <c r="BN34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BO34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9138,7 +9210,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:BM3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BN3:DH22 BO23:DH30 BN23:BN34">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BF3:DH3 BP4:DH30 BN4:BO34">
     <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D9B206-1F32-4E61-98BF-ABAB757F1246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC3396D-4FF9-4281-84CE-9710F6C58A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -877,7 +877,9 @@
       <c r="BO1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="BP1" s="1"/>
+      <c r="BP1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
       <c r="BS1" s="1"/>
@@ -1103,9 +1105,11 @@
         <v>46296</v>
       </c>
       <c r="BO2" s="1">
-        <v>46298</v>
-      </c>
-      <c r="BP2" s="1"/>
+        <v>46301</v>
+      </c>
+      <c r="BP2" s="1">
+        <v>46303</v>
+      </c>
       <c r="BQ2" s="1"/>
       <c r="BR2" s="1"/>
       <c r="BS2" s="1"/>
@@ -9210,7 +9214,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BF3:DH3 BP4:DH30 BN4:BO34">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BP4:DH30 BG4:BG34 BI4:BI34 BN4:BO34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33">
     <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC3396D-4FF9-4281-84CE-9710F6C58A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F885D2-F9B9-49B3-9977-BC27242E41C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -1338,7 +1338,9 @@
       <c r="BO3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP3" s="3"/>
+      <c r="BP3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ3" s="3"/>
       <c r="BR3" s="3"/>
       <c r="BS3" s="3"/>
@@ -1599,7 +1601,9 @@
       <c r="BO4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP4" s="3"/>
+      <c r="BP4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ4" s="3"/>
       <c r="BR4" s="3"/>
       <c r="BS4" s="3"/>
@@ -1860,7 +1864,9 @@
       <c r="BO5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP5" s="3"/>
+      <c r="BP5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ5" s="3"/>
       <c r="BR5" s="3"/>
       <c r="BS5" s="3"/>
@@ -2121,7 +2127,9 @@
       <c r="BO6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP6" s="3"/>
+      <c r="BP6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ6" s="3"/>
       <c r="BR6" s="3"/>
       <c r="BS6" s="3"/>
@@ -2382,7 +2390,9 @@
       <c r="BO7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP7" s="3"/>
+      <c r="BP7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ7" s="3"/>
       <c r="BR7" s="3"/>
       <c r="BS7" s="3"/>
@@ -2643,7 +2653,9 @@
       <c r="BO8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP8" s="3"/>
+      <c r="BP8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ8" s="3"/>
       <c r="BR8" s="3"/>
       <c r="BS8" s="3"/>
@@ -2904,7 +2916,9 @@
       <c r="BO9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP9" s="3"/>
+      <c r="BP9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ9" s="3"/>
       <c r="BR9" s="3"/>
       <c r="BS9" s="3"/>
@@ -3165,7 +3179,9 @@
       <c r="BO10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP10" s="3"/>
+      <c r="BP10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ10" s="3"/>
       <c r="BR10" s="3"/>
       <c r="BS10" s="3"/>
@@ -3417,7 +3433,9 @@
       <c r="BO11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP11" s="3"/>
+      <c r="BP11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ11" s="3"/>
       <c r="BR11" s="3"/>
       <c r="BS11" s="3"/>
@@ -3678,7 +3696,9 @@
       <c r="BO12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP12" s="3"/>
+      <c r="BP12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ12" s="3"/>
       <c r="BR12" s="3"/>
       <c r="BS12" s="3"/>
@@ -3939,7 +3959,9 @@
       <c r="BO13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP13" s="3"/>
+      <c r="BP13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ13" s="3"/>
       <c r="BR13" s="3"/>
       <c r="BS13" s="3"/>
@@ -4200,7 +4222,9 @@
       <c r="BO14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP14" s="3"/>
+      <c r="BP14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ14" s="3"/>
       <c r="BR14" s="3"/>
       <c r="BS14" s="3"/>
@@ -4461,7 +4485,9 @@
       <c r="BO15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP15" s="3"/>
+      <c r="BP15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ15" s="3"/>
       <c r="BR15" s="3"/>
       <c r="BS15" s="3"/>
@@ -4722,7 +4748,9 @@
       <c r="BO16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP16" s="3"/>
+      <c r="BP16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ16" s="3"/>
       <c r="BR16" s="3"/>
       <c r="BS16" s="3"/>
@@ -4962,7 +4990,9 @@
       <c r="BO17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP17" s="3"/>
+      <c r="BP17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ17" s="3"/>
       <c r="BR17" s="3"/>
       <c r="BS17" s="3"/>
@@ -5223,7 +5253,9 @@
       <c r="BO18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP18" s="3"/>
+      <c r="BP18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ18" s="3"/>
       <c r="BR18" s="3"/>
       <c r="BS18" s="3"/>
@@ -5484,7 +5516,9 @@
       <c r="BO19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP19" s="3"/>
+      <c r="BP19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ19" s="3"/>
       <c r="BR19" s="3"/>
       <c r="BS19" s="3"/>
@@ -5724,7 +5758,9 @@
       <c r="BO20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP20" s="3"/>
+      <c r="BP20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ20" s="3"/>
       <c r="BR20" s="3"/>
       <c r="BS20" s="3"/>
@@ -5985,7 +6021,9 @@
       <c r="BO21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP21" s="3"/>
+      <c r="BP21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ21" s="3"/>
       <c r="BR21" s="3"/>
       <c r="BS21" s="3"/>
@@ -6246,7 +6284,9 @@
       <c r="BO22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP22" s="3"/>
+      <c r="BP22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ22" s="3"/>
       <c r="BR22" s="3"/>
       <c r="BS22" s="3"/>
@@ -6507,7 +6547,9 @@
       <c r="BO23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP23" s="3"/>
+      <c r="BP23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ23" s="3"/>
       <c r="BR23" s="3"/>
       <c r="BS23" s="3"/>
@@ -6768,7 +6810,9 @@
       <c r="BO24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP24" s="3"/>
+      <c r="BP24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ24" s="3"/>
       <c r="BR24" s="3"/>
       <c r="BS24" s="3"/>
@@ -7029,7 +7073,9 @@
       <c r="BO25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP25" s="3"/>
+      <c r="BP25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ25" s="3"/>
       <c r="BR25" s="3"/>
       <c r="BS25" s="3"/>
@@ -7290,7 +7336,9 @@
       <c r="BO26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP26" s="3"/>
+      <c r="BP26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ26" s="3"/>
       <c r="BR26" s="3"/>
       <c r="BS26" s="3"/>
@@ -7551,7 +7599,9 @@
       <c r="BO27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP27" s="3"/>
+      <c r="BP27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ27" s="3"/>
       <c r="BR27" s="3"/>
       <c r="BS27" s="3"/>
@@ -7812,7 +7862,9 @@
       <c r="BO28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP28" s="3"/>
+      <c r="BP28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ28" s="3"/>
       <c r="BR28" s="3"/>
       <c r="BS28" s="3"/>
@@ -8064,7 +8116,9 @@
       <c r="BO29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP29" s="3"/>
+      <c r="BP29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ29" s="3"/>
       <c r="BR29" s="3"/>
       <c r="BS29" s="3"/>
@@ -8325,7 +8379,9 @@
       <c r="BO30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BP30" s="3"/>
+      <c r="BP30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BQ30" s="3"/>
       <c r="BR30" s="3"/>
       <c r="BS30" s="3"/>
@@ -8586,6 +8642,9 @@
       <c r="BO31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BP31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -8790,8 +8849,11 @@
       <c r="BO32" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BP32" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="33" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8994,8 +9056,11 @@
       <c r="BO33" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BP33" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="34" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9196,6 +9261,9 @@
         <v>31</v>
       </c>
       <c r="BO34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BP34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9214,7 +9282,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BP4:DH30 BG4:BG34 BI4:BI34 BN4:BO34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BP4:DH30 BG4:BG34 BI4:BI34 BN4:BO34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BP31:BP34">
     <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F885D2-F9B9-49B3-9977-BC27242E41C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4955594A-CF17-4340-B32B-6111C92F0415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="55">
   <si>
     <t>Aluno</t>
   </si>
@@ -209,7 +209,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +250,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -272,7 +279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -283,6 +290,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -880,7 +888,9 @@
       <c r="BP1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BQ1" s="1"/>
+      <c r="BQ1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="BR1" s="1"/>
       <c r="BS1" s="1"/>
       <c r="BT1" s="2"/>
@@ -1110,7 +1120,9 @@
       <c r="BP2" s="1">
         <v>46303</v>
       </c>
-      <c r="BQ2" s="1"/>
+      <c r="BQ2" s="1">
+        <v>46315</v>
+      </c>
       <c r="BR2" s="1"/>
       <c r="BS2" s="1"/>
       <c r="BT2" s="3"/>
@@ -1341,7 +1353,9 @@
       <c r="BP3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ3" s="3"/>
+      <c r="BQ3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR3" s="3"/>
       <c r="BS3" s="3"/>
       <c r="BT3" s="3"/>
@@ -1604,7 +1618,9 @@
       <c r="BP4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ4" s="3"/>
+      <c r="BQ4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR4" s="3"/>
       <c r="BS4" s="3"/>
       <c r="BT4" s="3"/>
@@ -1867,7 +1883,9 @@
       <c r="BP5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ5" s="3"/>
+      <c r="BQ5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR5" s="3"/>
       <c r="BS5" s="3"/>
       <c r="BT5" s="3"/>
@@ -2130,7 +2148,9 @@
       <c r="BP6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ6" s="3"/>
+      <c r="BQ6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR6" s="3"/>
       <c r="BS6" s="3"/>
       <c r="BT6" s="3"/>
@@ -2393,7 +2413,9 @@
       <c r="BP7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ7" s="3"/>
+      <c r="BQ7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR7" s="3"/>
       <c r="BS7" s="3"/>
       <c r="BT7" s="3"/>
@@ -2656,7 +2678,9 @@
       <c r="BP8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ8" s="3"/>
+      <c r="BQ8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR8" s="3"/>
       <c r="BS8" s="3"/>
       <c r="BT8" s="3"/>
@@ -2919,7 +2943,9 @@
       <c r="BP9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ9" s="3"/>
+      <c r="BQ9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR9" s="3"/>
       <c r="BS9" s="3"/>
       <c r="BT9" s="3"/>
@@ -3182,7 +3208,9 @@
       <c r="BP10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ10" s="3"/>
+      <c r="BQ10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR10" s="3"/>
       <c r="BS10" s="3"/>
       <c r="BT10" s="3"/>
@@ -3436,7 +3464,9 @@
       <c r="BP11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ11" s="3"/>
+      <c r="BQ11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR11" s="3"/>
       <c r="BS11" s="3"/>
       <c r="BT11" s="3"/>
@@ -3699,7 +3729,9 @@
       <c r="BP12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ12" s="3"/>
+      <c r="BQ12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR12" s="3"/>
       <c r="BS12" s="3"/>
       <c r="BT12" s="3"/>
@@ -3962,7 +3994,9 @@
       <c r="BP13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ13" s="3"/>
+      <c r="BQ13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR13" s="3"/>
       <c r="BS13" s="3"/>
       <c r="BT13" s="3"/>
@@ -4225,7 +4259,9 @@
       <c r="BP14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ14" s="3"/>
+      <c r="BQ14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR14" s="3"/>
       <c r="BS14" s="3"/>
       <c r="BT14" s="3"/>
@@ -4488,7 +4524,9 @@
       <c r="BP15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ15" s="3"/>
+      <c r="BQ15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR15" s="3"/>
       <c r="BS15" s="3"/>
       <c r="BT15" s="3"/>
@@ -4751,7 +4789,9 @@
       <c r="BP16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ16" s="3"/>
+      <c r="BQ16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR16" s="3"/>
       <c r="BS16" s="3"/>
       <c r="BT16" s="3"/>
@@ -4993,7 +5033,9 @@
       <c r="BP17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ17" s="3"/>
+      <c r="BQ17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR17" s="3"/>
       <c r="BS17" s="3"/>
       <c r="BT17" s="3"/>
@@ -5256,7 +5298,9 @@
       <c r="BP18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ18" s="3"/>
+      <c r="BQ18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR18" s="3"/>
       <c r="BS18" s="3"/>
       <c r="BT18" s="3"/>
@@ -5519,7 +5563,9 @@
       <c r="BP19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ19" s="3"/>
+      <c r="BQ19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR19" s="3"/>
       <c r="BS19" s="3"/>
       <c r="BT19" s="3"/>
@@ -5761,7 +5807,9 @@
       <c r="BP20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ20" s="3"/>
+      <c r="BQ20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR20" s="3"/>
       <c r="BS20" s="3"/>
       <c r="BT20" s="3"/>
@@ -6024,7 +6072,9 @@
       <c r="BP21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ21" s="3"/>
+      <c r="BQ21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR21" s="3"/>
       <c r="BS21" s="3"/>
       <c r="BT21" s="3"/>
@@ -6287,7 +6337,9 @@
       <c r="BP22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ22" s="3"/>
+      <c r="BQ22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR22" s="3"/>
       <c r="BS22" s="3"/>
       <c r="BT22" s="3"/>
@@ -6550,7 +6602,9 @@
       <c r="BP23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ23" s="3"/>
+      <c r="BQ23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR23" s="3"/>
       <c r="BS23" s="3"/>
       <c r="BT23" s="3"/>
@@ -6813,7 +6867,9 @@
       <c r="BP24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ24" s="3"/>
+      <c r="BQ24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR24" s="3"/>
       <c r="BS24" s="3"/>
       <c r="BT24" s="3"/>
@@ -7076,7 +7132,9 @@
       <c r="BP25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ25" s="3"/>
+      <c r="BQ25" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BR25" s="3"/>
       <c r="BS25" s="3"/>
       <c r="BT25" s="3"/>
@@ -7339,7 +7397,9 @@
       <c r="BP26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ26" s="3"/>
+      <c r="BQ26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR26" s="3"/>
       <c r="BS26" s="3"/>
       <c r="BT26" s="3"/>
@@ -7602,7 +7662,9 @@
       <c r="BP27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ27" s="3"/>
+      <c r="BQ27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR27" s="3"/>
       <c r="BS27" s="3"/>
       <c r="BT27" s="3"/>
@@ -7865,7 +7927,9 @@
       <c r="BP28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ28" s="3"/>
+      <c r="BQ28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR28" s="3"/>
       <c r="BS28" s="3"/>
       <c r="BT28" s="3"/>
@@ -8119,7 +8183,9 @@
       <c r="BP29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ29" s="3"/>
+      <c r="BQ29" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BR29" s="3"/>
       <c r="BS29" s="3"/>
       <c r="BT29" s="3"/>
@@ -8382,7 +8448,9 @@
       <c r="BP30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ30" s="3"/>
+      <c r="BQ30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BR30" s="3"/>
       <c r="BS30" s="3"/>
       <c r="BT30" s="3"/>
@@ -8645,6 +8713,9 @@
       <c r="BP31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BQ31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -8852,8 +8923,11 @@
       <c r="BP32" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BQ32" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="33" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -9059,8 +9133,11 @@
       <c r="BP33" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BQ33" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="34" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9264,6 +9341,9 @@
         <v>31</v>
       </c>
       <c r="BP34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BQ34" s="8" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9282,7 +9362,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BP4:DH30 BG4:BG34 BI4:BI34 BN4:BO34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BP31:BP34">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BF3:DH3 BR4:DH30 BN4:BQ34">
     <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4955594A-CF17-4340-B32B-6111C92F0415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F58B12-536B-4349-A4B2-C7D75B1E9CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="56">
   <si>
     <t>Aluno</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>saida antecipada</t>
+  </si>
+  <si>
+    <t>REMOTO</t>
   </si>
 </sst>
 </file>
@@ -686,10 +689,14 @@
     <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="58" width="7.7109375" customWidth="1"/>
-    <col min="59" max="59" width="8.5703125" customWidth="1"/>
-    <col min="60" max="107" width="7.7109375" customWidth="1"/>
+    <col min="53" max="56" width="7" bestFit="1" customWidth="1"/>
+    <col min="57" max="58" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="65" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="66" max="68" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="69" max="70" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:124" x14ac:dyDescent="0.25">
@@ -891,9 +898,15 @@
       <c r="BQ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="BR1" s="1"/>
-      <c r="BS1" s="1"/>
-      <c r="BT1" s="2"/>
+      <c r="BR1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT1" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
       <c r="BW1" s="2"/>
@@ -1121,11 +1134,17 @@
         <v>46303</v>
       </c>
       <c r="BQ2" s="1">
+        <v>46308</v>
+      </c>
+      <c r="BR2" s="1">
+        <v>46310</v>
+      </c>
+      <c r="BS2" s="1">
         <v>46315</v>
       </c>
-      <c r="BR2" s="1"/>
-      <c r="BS2" s="1"/>
-      <c r="BT2" s="3"/>
+      <c r="BT2" s="2">
+        <v>46317</v>
+      </c>
       <c r="BU2" s="3"/>
       <c r="BV2" s="3"/>
       <c r="BW2" s="3"/>
@@ -1354,11 +1373,15 @@
         <v>31</v>
       </c>
       <c r="BQ3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR3" s="3"/>
-      <c r="BS3" s="3"/>
-      <c r="BT3" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BT3" s="8"/>
       <c r="BU3" s="3"/>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
@@ -1619,10 +1642,14 @@
         <v>31</v>
       </c>
       <c r="BQ4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR4" s="3"/>
-      <c r="BS4" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT4" s="3"/>
       <c r="BU4" s="3"/>
       <c r="BV4" s="3"/>
@@ -1884,10 +1911,14 @@
         <v>31</v>
       </c>
       <c r="BQ5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR5" s="3"/>
-      <c r="BS5" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS5" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="BT5" s="3"/>
       <c r="BU5" s="3"/>
       <c r="BV5" s="3"/>
@@ -2149,10 +2180,14 @@
         <v>31</v>
       </c>
       <c r="BQ6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR6" s="3"/>
-      <c r="BS6" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT6" s="3"/>
       <c r="BU6" s="3"/>
       <c r="BV6" s="3"/>
@@ -2414,10 +2449,14 @@
         <v>31</v>
       </c>
       <c r="BQ7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR7" s="3"/>
-      <c r="BS7" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT7" s="3"/>
       <c r="BU7" s="3"/>
       <c r="BV7" s="3"/>
@@ -2679,10 +2718,14 @@
         <v>31</v>
       </c>
       <c r="BQ8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR8" s="3"/>
-      <c r="BS8" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT8" s="3"/>
       <c r="BU8" s="3"/>
       <c r="BV8" s="3"/>
@@ -2944,10 +2987,14 @@
         <v>31</v>
       </c>
       <c r="BQ9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR9" s="3"/>
-      <c r="BS9" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT9" s="3"/>
       <c r="BU9" s="3"/>
       <c r="BV9" s="3"/>
@@ -3209,10 +3256,14 @@
         <v>31</v>
       </c>
       <c r="BQ10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR10" s="3"/>
-      <c r="BS10" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS10" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="BT10" s="3"/>
       <c r="BU10" s="3"/>
       <c r="BV10" s="3"/>
@@ -3465,10 +3516,14 @@
         <v>31</v>
       </c>
       <c r="BQ11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR11" s="3"/>
-      <c r="BS11" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT11" s="3"/>
       <c r="BU11" s="3"/>
       <c r="BV11" s="3"/>
@@ -3730,10 +3785,14 @@
         <v>31</v>
       </c>
       <c r="BQ12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR12" s="3"/>
-      <c r="BS12" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT12" s="3"/>
       <c r="BU12" s="3"/>
       <c r="BV12" s="3"/>
@@ -3995,10 +4054,14 @@
         <v>31</v>
       </c>
       <c r="BQ13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR13" s="3"/>
-      <c r="BS13" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT13" s="3"/>
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
@@ -4260,10 +4323,14 @@
         <v>31</v>
       </c>
       <c r="BQ14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR14" s="3"/>
-      <c r="BS14" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT14" s="3"/>
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
@@ -4525,10 +4592,14 @@
         <v>31</v>
       </c>
       <c r="BQ15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR15" s="3"/>
-      <c r="BS15" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT15" s="3"/>
       <c r="BU15" s="3"/>
       <c r="BV15" s="3"/>
@@ -4790,10 +4861,14 @@
         <v>31</v>
       </c>
       <c r="BQ16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR16" s="3"/>
-      <c r="BS16" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT16" s="3"/>
       <c r="BU16" s="3"/>
       <c r="BV16" s="3"/>
@@ -5034,10 +5109,14 @@
         <v>31</v>
       </c>
       <c r="BQ17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR17" s="3"/>
-      <c r="BS17" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT17" s="3"/>
       <c r="BU17" s="3"/>
       <c r="BV17" s="3"/>
@@ -5299,10 +5378,14 @@
         <v>31</v>
       </c>
       <c r="BQ18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR18" s="3"/>
-      <c r="BS18" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT18" s="3"/>
       <c r="BU18" s="3"/>
       <c r="BV18" s="3"/>
@@ -5564,10 +5647,14 @@
         <v>31</v>
       </c>
       <c r="BQ19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR19" s="3"/>
-      <c r="BS19" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT19" s="3"/>
       <c r="BU19" s="3"/>
       <c r="BV19" s="3"/>
@@ -5808,10 +5895,14 @@
         <v>31</v>
       </c>
       <c r="BQ20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR20" s="3"/>
-      <c r="BS20" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT20" s="3"/>
       <c r="BU20" s="3"/>
       <c r="BV20" s="3"/>
@@ -6073,10 +6164,14 @@
         <v>31</v>
       </c>
       <c r="BQ21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR21" s="3"/>
-      <c r="BS21" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT21" s="3"/>
       <c r="BU21" s="3"/>
       <c r="BV21" s="3"/>
@@ -6338,10 +6433,14 @@
         <v>31</v>
       </c>
       <c r="BQ22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR22" s="3"/>
-      <c r="BS22" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT22" s="3"/>
       <c r="BU22" s="3"/>
       <c r="BV22" s="3"/>
@@ -6603,10 +6702,14 @@
         <v>31</v>
       </c>
       <c r="BQ23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR23" s="3"/>
-      <c r="BS23" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT23" s="3"/>
       <c r="BU23" s="3"/>
       <c r="BV23" s="3"/>
@@ -6868,10 +6971,14 @@
         <v>31</v>
       </c>
       <c r="BQ24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR24" s="3"/>
-      <c r="BS24" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT24" s="3"/>
       <c r="BU24" s="3"/>
       <c r="BV24" s="3"/>
@@ -7133,10 +7240,14 @@
         <v>31</v>
       </c>
       <c r="BQ25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BR25" s="3"/>
-      <c r="BS25" s="3"/>
       <c r="BT25" s="3"/>
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
@@ -7398,10 +7509,14 @@
         <v>31</v>
       </c>
       <c r="BQ26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR26" s="3"/>
-      <c r="BS26" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT26" s="3"/>
       <c r="BU26" s="3"/>
       <c r="BV26" s="3"/>
@@ -7663,10 +7778,14 @@
         <v>31</v>
       </c>
       <c r="BQ27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR27" s="3"/>
-      <c r="BS27" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT27" s="3"/>
       <c r="BU27" s="3"/>
       <c r="BV27" s="3"/>
@@ -7928,10 +8047,14 @@
         <v>31</v>
       </c>
       <c r="BQ28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR28" s="3"/>
-      <c r="BS28" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT28" s="3"/>
       <c r="BU28" s="3"/>
       <c r="BV28" s="3"/>
@@ -8184,10 +8307,14 @@
         <v>31</v>
       </c>
       <c r="BQ29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BR29" s="3"/>
-      <c r="BS29" s="3"/>
       <c r="BT29" s="3"/>
       <c r="BU29" s="3"/>
       <c r="BV29" s="3"/>
@@ -8449,10 +8576,14 @@
         <v>31</v>
       </c>
       <c r="BQ30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="BR30" s="3"/>
-      <c r="BS30" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="BR30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT30" s="3"/>
       <c r="BU30" s="3"/>
       <c r="BV30" s="3"/>
@@ -8714,6 +8845,12 @@
         <v>31</v>
       </c>
       <c r="BQ31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS31" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8924,10 +9061,16 @@
         <v>31</v>
       </c>
       <c r="BQ32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS32" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -9134,10 +9277,16 @@
         <v>31</v>
       </c>
       <c r="BQ33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS33" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9343,7 +9492,13 @@
       <c r="BP34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BQ34" s="8" t="s">
+      <c r="BQ34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9352,7 +9507,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G31:I32">
+  <conditionalFormatting sqref="G31:I32 BT3:DH3 BS3:BS34 BF3:BR3 BN4:BR34">
     <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9362,7 +9517,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BF3:DH3 BR4:DH30 BN4:BQ34">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BS4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33">
     <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F58B12-536B-4349-A4B2-C7D75B1E9CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA03BDE-F26F-42EF-B641-A7030DD190AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="56">
   <si>
     <t>Aluno</t>
   </si>
@@ -212,7 +212,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,13 +253,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -282,7 +275,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -293,7 +286,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1381,7 +1373,9 @@
       <c r="BS3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT3" s="8"/>
+      <c r="BT3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU3" s="3"/>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
@@ -1650,7 +1644,9 @@
       <c r="BS4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT4" s="3"/>
+      <c r="BT4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU4" s="3"/>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
@@ -1919,7 +1915,9 @@
       <c r="BS5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BT5" s="3"/>
+      <c r="BT5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU5" s="3"/>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
@@ -2188,7 +2186,9 @@
       <c r="BS6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT6" s="3"/>
+      <c r="BT6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU6" s="3"/>
       <c r="BV6" s="3"/>
       <c r="BW6" s="3"/>
@@ -2457,7 +2457,9 @@
       <c r="BS7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT7" s="3"/>
+      <c r="BT7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU7" s="3"/>
       <c r="BV7" s="3"/>
       <c r="BW7" s="3"/>
@@ -2726,7 +2728,9 @@
       <c r="BS8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT8" s="3"/>
+      <c r="BT8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU8" s="3"/>
       <c r="BV8" s="3"/>
       <c r="BW8" s="3"/>
@@ -2995,7 +2999,9 @@
       <c r="BS9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT9" s="3"/>
+      <c r="BT9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU9" s="3"/>
       <c r="BV9" s="3"/>
       <c r="BW9" s="3"/>
@@ -3264,7 +3270,9 @@
       <c r="BS10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BT10" s="3"/>
+      <c r="BT10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU10" s="3"/>
       <c r="BV10" s="3"/>
       <c r="BW10" s="3"/>
@@ -3524,7 +3532,9 @@
       <c r="BS11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT11" s="3"/>
+      <c r="BT11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU11" s="3"/>
       <c r="BV11" s="3"/>
       <c r="BW11" s="3"/>
@@ -3793,7 +3803,9 @@
       <c r="BS12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT12" s="3"/>
+      <c r="BT12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU12" s="3"/>
       <c r="BV12" s="3"/>
       <c r="BW12" s="3"/>
@@ -4062,7 +4074,9 @@
       <c r="BS13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT13" s="3"/>
+      <c r="BT13" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
       <c r="BW13" s="3"/>
@@ -4331,7 +4345,9 @@
       <c r="BS14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT14" s="3"/>
+      <c r="BT14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
       <c r="BW14" s="3"/>
@@ -4600,7 +4616,9 @@
       <c r="BS15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT15" s="3"/>
+      <c r="BT15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU15" s="3"/>
       <c r="BV15" s="3"/>
       <c r="BW15" s="3"/>
@@ -4869,7 +4887,9 @@
       <c r="BS16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT16" s="3"/>
+      <c r="BT16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU16" s="3"/>
       <c r="BV16" s="3"/>
       <c r="BW16" s="3"/>
@@ -5117,7 +5137,9 @@
       <c r="BS17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT17" s="3"/>
+      <c r="BT17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU17" s="3"/>
       <c r="BV17" s="3"/>
       <c r="BW17" s="3"/>
@@ -5386,7 +5408,9 @@
       <c r="BS18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT18" s="3"/>
+      <c r="BT18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU18" s="3"/>
       <c r="BV18" s="3"/>
       <c r="BW18" s="3"/>
@@ -5655,7 +5679,9 @@
       <c r="BS19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT19" s="3"/>
+      <c r="BT19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU19" s="3"/>
       <c r="BV19" s="3"/>
       <c r="BW19" s="3"/>
@@ -5903,7 +5929,9 @@
       <c r="BS20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT20" s="3"/>
+      <c r="BT20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU20" s="3"/>
       <c r="BV20" s="3"/>
       <c r="BW20" s="3"/>
@@ -6172,7 +6200,9 @@
       <c r="BS21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT21" s="3"/>
+      <c r="BT21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU21" s="3"/>
       <c r="BV21" s="3"/>
       <c r="BW21" s="3"/>
@@ -6441,7 +6471,9 @@
       <c r="BS22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT22" s="3"/>
+      <c r="BT22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU22" s="3"/>
       <c r="BV22" s="3"/>
       <c r="BW22" s="3"/>
@@ -6710,7 +6742,9 @@
       <c r="BS23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT23" s="3"/>
+      <c r="BT23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU23" s="3"/>
       <c r="BV23" s="3"/>
       <c r="BW23" s="3"/>
@@ -6979,7 +7013,9 @@
       <c r="BS24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT24" s="3"/>
+      <c r="BT24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU24" s="3"/>
       <c r="BV24" s="3"/>
       <c r="BW24" s="3"/>
@@ -7248,7 +7284,9 @@
       <c r="BS25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BT25" s="3"/>
+      <c r="BT25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
       <c r="BW25" s="3"/>
@@ -7517,7 +7555,9 @@
       <c r="BS26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT26" s="3"/>
+      <c r="BT26" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BU26" s="3"/>
       <c r="BV26" s="3"/>
       <c r="BW26" s="3"/>
@@ -7786,7 +7826,9 @@
       <c r="BS27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT27" s="3"/>
+      <c r="BT27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU27" s="3"/>
       <c r="BV27" s="3"/>
       <c r="BW27" s="3"/>
@@ -8055,7 +8097,9 @@
       <c r="BS28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT28" s="3"/>
+      <c r="BT28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU28" s="3"/>
       <c r="BV28" s="3"/>
       <c r="BW28" s="3"/>
@@ -8315,7 +8359,9 @@
       <c r="BS29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BT29" s="3"/>
+      <c r="BT29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU29" s="3"/>
       <c r="BV29" s="3"/>
       <c r="BW29" s="3"/>
@@ -8584,7 +8630,9 @@
       <c r="BS30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BT30" s="3"/>
+      <c r="BT30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BU30" s="3"/>
       <c r="BV30" s="3"/>
       <c r="BW30" s="3"/>
@@ -8853,6 +8901,9 @@
       <c r="BS31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BT31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -9069,8 +9120,11 @@
       <c r="BS32" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BT32" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="33" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -9285,8 +9339,11 @@
       <c r="BS33" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BT33" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="34" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9499,6 +9556,9 @@
         <v>55</v>
       </c>
       <c r="BS34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BT34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9507,34 +9567,34 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G31:I32 BT3:DH3 BS3:BS34 BF3:BR3 BN4:BR34">
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+  <conditionalFormatting sqref="U3:AS34">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BS4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33">
-    <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BS4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 BT31:BT34 H33:I33">
+    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BF3:BR3 BT3:DH3 BS3:BS34 BN4:BR34 G31:I32">
+    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
+      <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH3:BI34">

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4955594A-CF17-4340-B32B-6111C92F0415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8A5A9E-8313-4635-AE35-D445158E6139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="56">
   <si>
     <t>Aluno</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>saida antecipada</t>
+  </si>
+  <si>
+    <t>QUA</t>
   </si>
 </sst>
 </file>
@@ -891,8 +894,12 @@
       <c r="BQ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="BR1" s="1"/>
-      <c r="BS1" s="1"/>
+      <c r="BR1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
@@ -1123,8 +1130,12 @@
       <c r="BQ2" s="1">
         <v>46315</v>
       </c>
-      <c r="BR2" s="1"/>
-      <c r="BS2" s="1"/>
+      <c r="BR2" s="1">
+        <v>46317</v>
+      </c>
+      <c r="BS2" s="1">
+        <v>46322</v>
+      </c>
       <c r="BT2" s="3"/>
       <c r="BU2" s="3"/>
       <c r="BV2" s="3"/>
@@ -1356,8 +1367,12 @@
       <c r="BQ3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR3" s="3"/>
-      <c r="BS3" s="3"/>
+      <c r="BR3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT3" s="3"/>
       <c r="BU3" s="3"/>
       <c r="BV3" s="3"/>
@@ -1621,8 +1636,12 @@
       <c r="BQ4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR4" s="3"/>
-      <c r="BS4" s="3"/>
+      <c r="BR4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT4" s="3"/>
       <c r="BU4" s="3"/>
       <c r="BV4" s="3"/>
@@ -1886,8 +1905,12 @@
       <c r="BQ5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR5" s="3"/>
-      <c r="BS5" s="3"/>
+      <c r="BR5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT5" s="3"/>
       <c r="BU5" s="3"/>
       <c r="BV5" s="3"/>
@@ -2151,8 +2174,12 @@
       <c r="BQ6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR6" s="3"/>
-      <c r="BS6" s="3"/>
+      <c r="BR6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT6" s="3"/>
       <c r="BU6" s="3"/>
       <c r="BV6" s="3"/>
@@ -2416,8 +2443,12 @@
       <c r="BQ7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR7" s="3"/>
-      <c r="BS7" s="3"/>
+      <c r="BR7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT7" s="3"/>
       <c r="BU7" s="3"/>
       <c r="BV7" s="3"/>
@@ -2681,8 +2712,12 @@
       <c r="BQ8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR8" s="3"/>
-      <c r="BS8" s="3"/>
+      <c r="BR8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT8" s="3"/>
       <c r="BU8" s="3"/>
       <c r="BV8" s="3"/>
@@ -2946,8 +2981,12 @@
       <c r="BQ9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR9" s="3"/>
-      <c r="BS9" s="3"/>
+      <c r="BR9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS9" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BT9" s="3"/>
       <c r="BU9" s="3"/>
       <c r="BV9" s="3"/>
@@ -3211,8 +3250,12 @@
       <c r="BQ10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR10" s="3"/>
-      <c r="BS10" s="3"/>
+      <c r="BR10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT10" s="3"/>
       <c r="BU10" s="3"/>
       <c r="BV10" s="3"/>
@@ -3467,8 +3510,12 @@
       <c r="BQ11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR11" s="3"/>
-      <c r="BS11" s="3"/>
+      <c r="BR11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT11" s="3"/>
       <c r="BU11" s="3"/>
       <c r="BV11" s="3"/>
@@ -3732,8 +3779,12 @@
       <c r="BQ12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR12" s="3"/>
-      <c r="BS12" s="3"/>
+      <c r="BR12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT12" s="3"/>
       <c r="BU12" s="3"/>
       <c r="BV12" s="3"/>
@@ -3997,8 +4048,12 @@
       <c r="BQ13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR13" s="3"/>
-      <c r="BS13" s="3"/>
+      <c r="BR13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT13" s="3"/>
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
@@ -4262,8 +4317,12 @@
       <c r="BQ14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR14" s="3"/>
-      <c r="BS14" s="3"/>
+      <c r="BR14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT14" s="3"/>
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
@@ -4527,8 +4586,12 @@
       <c r="BQ15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR15" s="3"/>
-      <c r="BS15" s="3"/>
+      <c r="BR15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT15" s="3"/>
       <c r="BU15" s="3"/>
       <c r="BV15" s="3"/>
@@ -4792,8 +4855,12 @@
       <c r="BQ16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR16" s="3"/>
-      <c r="BS16" s="3"/>
+      <c r="BR16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT16" s="3"/>
       <c r="BU16" s="3"/>
       <c r="BV16" s="3"/>
@@ -5036,8 +5103,12 @@
       <c r="BQ17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR17" s="3"/>
-      <c r="BS17" s="3"/>
+      <c r="BR17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT17" s="3"/>
       <c r="BU17" s="3"/>
       <c r="BV17" s="3"/>
@@ -5301,8 +5372,12 @@
       <c r="BQ18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR18" s="3"/>
-      <c r="BS18" s="3"/>
+      <c r="BR18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT18" s="3"/>
       <c r="BU18" s="3"/>
       <c r="BV18" s="3"/>
@@ -5566,8 +5641,12 @@
       <c r="BQ19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR19" s="3"/>
-      <c r="BS19" s="3"/>
+      <c r="BR19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT19" s="3"/>
       <c r="BU19" s="3"/>
       <c r="BV19" s="3"/>
@@ -5810,8 +5889,12 @@
       <c r="BQ20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR20" s="3"/>
-      <c r="BS20" s="3"/>
+      <c r="BR20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT20" s="3"/>
       <c r="BU20" s="3"/>
       <c r="BV20" s="3"/>
@@ -6075,8 +6158,12 @@
       <c r="BQ21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR21" s="3"/>
-      <c r="BS21" s="3"/>
+      <c r="BR21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT21" s="3"/>
       <c r="BU21" s="3"/>
       <c r="BV21" s="3"/>
@@ -6340,8 +6427,12 @@
       <c r="BQ22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR22" s="3"/>
-      <c r="BS22" s="3"/>
+      <c r="BR22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT22" s="3"/>
       <c r="BU22" s="3"/>
       <c r="BV22" s="3"/>
@@ -6605,8 +6696,12 @@
       <c r="BQ23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR23" s="3"/>
-      <c r="BS23" s="3"/>
+      <c r="BR23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT23" s="3"/>
       <c r="BU23" s="3"/>
       <c r="BV23" s="3"/>
@@ -6870,8 +6965,12 @@
       <c r="BQ24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR24" s="3"/>
-      <c r="BS24" s="3"/>
+      <c r="BR24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT24" s="3"/>
       <c r="BU24" s="3"/>
       <c r="BV24" s="3"/>
@@ -7135,8 +7234,12 @@
       <c r="BQ25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BR25" s="3"/>
-      <c r="BS25" s="3"/>
+      <c r="BR25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT25" s="3"/>
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
@@ -7400,8 +7503,12 @@
       <c r="BQ26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR26" s="3"/>
-      <c r="BS26" s="3"/>
+      <c r="BR26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT26" s="3"/>
       <c r="BU26" s="3"/>
       <c r="BV26" s="3"/>
@@ -7665,8 +7772,12 @@
       <c r="BQ27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR27" s="3"/>
-      <c r="BS27" s="3"/>
+      <c r="BR27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT27" s="3"/>
       <c r="BU27" s="3"/>
       <c r="BV27" s="3"/>
@@ -7930,8 +8041,12 @@
       <c r="BQ28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR28" s="3"/>
-      <c r="BS28" s="3"/>
+      <c r="BR28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT28" s="3"/>
       <c r="BU28" s="3"/>
       <c r="BV28" s="3"/>
@@ -8186,8 +8301,12 @@
       <c r="BQ29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BR29" s="3"/>
-      <c r="BS29" s="3"/>
+      <c r="BR29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS29" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BT29" s="3"/>
       <c r="BU29" s="3"/>
       <c r="BV29" s="3"/>
@@ -8451,8 +8570,12 @@
       <c r="BQ30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BR30" s="3"/>
-      <c r="BS30" s="3"/>
+      <c r="BR30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BT30" s="3"/>
       <c r="BU30" s="3"/>
       <c r="BV30" s="3"/>
@@ -8716,6 +8839,12 @@
       <c r="BQ31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BR31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -8926,8 +9055,14 @@
       <c r="BQ32" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BR32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS32" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -9136,8 +9271,14 @@
       <c r="BQ33" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BR33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS33" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9344,6 +9485,12 @@
         <v>31</v>
       </c>
       <c r="BQ34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BS34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9362,7 +9509,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BF3:DH3 BR4:DH30 BN4:BQ34">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BT4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BF3:DH3 BN4:BS34">
     <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64369648-7257-4B04-9813-051C30F0F84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4912965D-9497-476E-BF15-F8FE769ABD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6450" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="56">
   <si>
     <t>Aluno</t>
   </si>
@@ -902,8 +902,12 @@
       <c r="BU1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="BV1" s="2"/>
-      <c r="BW1" s="2"/>
+      <c r="BV1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="BW1" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="BX1" s="2"/>
       <c r="BY1" s="2"/>
       <c r="BZ1" s="2"/>
@@ -1142,8 +1146,12 @@
       <c r="BU2" s="2">
         <v>46322</v>
       </c>
-      <c r="BV2" s="3"/>
-      <c r="BW2" s="3"/>
+      <c r="BV2" s="2">
+        <v>46322</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>46324</v>
+      </c>
       <c r="BX2" s="3"/>
       <c r="BY2" s="3"/>
       <c r="BZ2" s="3"/>
@@ -1383,7 +1391,9 @@
       <c r="BU3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV3" s="3"/>
+      <c r="BV3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
       <c r="BY3" s="3"/>
@@ -1656,7 +1666,9 @@
       <c r="BU4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV4" s="3"/>
+      <c r="BV4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
       <c r="BY4" s="3"/>
@@ -1929,7 +1941,9 @@
       <c r="BU5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV5" s="3"/>
+      <c r="BV5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
       <c r="BY5" s="3"/>
@@ -2202,7 +2216,9 @@
       <c r="BU6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV6" s="3"/>
+      <c r="BV6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW6" s="3"/>
       <c r="BX6" s="3"/>
       <c r="BY6" s="3"/>
@@ -2475,7 +2491,9 @@
       <c r="BU7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV7" s="3"/>
+      <c r="BV7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW7" s="3"/>
       <c r="BX7" s="3"/>
       <c r="BY7" s="3"/>
@@ -2748,7 +2766,9 @@
       <c r="BU8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV8" s="3"/>
+      <c r="BV8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW8" s="3"/>
       <c r="BX8" s="3"/>
       <c r="BY8" s="3"/>
@@ -3021,7 +3041,9 @@
       <c r="BU9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BV9" s="3"/>
+      <c r="BV9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW9" s="3"/>
       <c r="BX9" s="3"/>
       <c r="BY9" s="3"/>
@@ -3294,7 +3316,9 @@
       <c r="BU10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV10" s="3"/>
+      <c r="BV10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW10" s="3"/>
       <c r="BX10" s="3"/>
       <c r="BY10" s="3"/>
@@ -3558,7 +3582,9 @@
       <c r="BU11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV11" s="3"/>
+      <c r="BV11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW11" s="3"/>
       <c r="BX11" s="3"/>
       <c r="BY11" s="3"/>
@@ -3831,7 +3857,9 @@
       <c r="BU12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV12" s="3"/>
+      <c r="BV12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW12" s="3"/>
       <c r="BX12" s="3"/>
       <c r="BY12" s="3"/>
@@ -4104,7 +4132,9 @@
       <c r="BU13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV13" s="3"/>
+      <c r="BV13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW13" s="3"/>
       <c r="BX13" s="3"/>
       <c r="BY13" s="3"/>
@@ -4377,7 +4407,9 @@
       <c r="BU14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV14" s="3"/>
+      <c r="BV14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW14" s="3"/>
       <c r="BX14" s="3"/>
       <c r="BY14" s="3"/>
@@ -4650,7 +4682,9 @@
       <c r="BU15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV15" s="3"/>
+      <c r="BV15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW15" s="3"/>
       <c r="BX15" s="3"/>
       <c r="BY15" s="3"/>
@@ -4923,7 +4957,9 @@
       <c r="BU16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV16" s="3"/>
+      <c r="BV16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW16" s="3"/>
       <c r="BX16" s="3"/>
       <c r="BY16" s="3"/>
@@ -5175,7 +5211,9 @@
       <c r="BU17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV17" s="3"/>
+      <c r="BV17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW17" s="3"/>
       <c r="BX17" s="3"/>
       <c r="BY17" s="3"/>
@@ -5448,7 +5486,9 @@
       <c r="BU18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV18" s="3"/>
+      <c r="BV18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW18" s="3"/>
       <c r="BX18" s="3"/>
       <c r="BY18" s="3"/>
@@ -5721,7 +5761,9 @@
       <c r="BU19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV19" s="3"/>
+      <c r="BV19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW19" s="3"/>
       <c r="BX19" s="3"/>
       <c r="BY19" s="3"/>
@@ -5973,7 +6015,9 @@
       <c r="BU20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV20" s="3"/>
+      <c r="BV20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW20" s="3"/>
       <c r="BX20" s="3"/>
       <c r="BY20" s="3"/>
@@ -6246,7 +6290,9 @@
       <c r="BU21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV21" s="3"/>
+      <c r="BV21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW21" s="3"/>
       <c r="BX21" s="3"/>
       <c r="BY21" s="3"/>
@@ -6519,7 +6565,9 @@
       <c r="BU22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV22" s="3"/>
+      <c r="BV22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW22" s="3"/>
       <c r="BX22" s="3"/>
       <c r="BY22" s="3"/>
@@ -6792,7 +6840,9 @@
       <c r="BU23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV23" s="3"/>
+      <c r="BV23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW23" s="3"/>
       <c r="BX23" s="3"/>
       <c r="BY23" s="3"/>
@@ -7065,7 +7115,9 @@
       <c r="BU24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV24" s="3"/>
+      <c r="BV24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW24" s="3"/>
       <c r="BX24" s="3"/>
       <c r="BY24" s="3"/>
@@ -7338,7 +7390,9 @@
       <c r="BU25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV25" s="3"/>
+      <c r="BV25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW25" s="3"/>
       <c r="BX25" s="3"/>
       <c r="BY25" s="3"/>
@@ -7611,7 +7665,9 @@
       <c r="BU26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV26" s="3"/>
+      <c r="BV26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW26" s="3"/>
       <c r="BX26" s="3"/>
       <c r="BY26" s="3"/>
@@ -7884,7 +7940,9 @@
       <c r="BU27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV27" s="3"/>
+      <c r="BV27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW27" s="3"/>
       <c r="BX27" s="3"/>
       <c r="BY27" s="3"/>
@@ -8157,7 +8215,9 @@
       <c r="BU28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV28" s="3"/>
+      <c r="BV28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW28" s="3"/>
       <c r="BX28" s="3"/>
       <c r="BY28" s="3"/>
@@ -8421,7 +8481,9 @@
       <c r="BU29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BV29" s="3"/>
+      <c r="BV29" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BW29" s="3"/>
       <c r="BX29" s="3"/>
       <c r="BY29" s="3"/>
@@ -8694,7 +8756,9 @@
       <c r="BU30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BV30" s="3"/>
+      <c r="BV30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BW30" s="3"/>
       <c r="BX30" s="3"/>
       <c r="BY30" s="3"/>
@@ -8967,6 +9031,9 @@
       <c r="BU31" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BV31" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -9189,8 +9256,11 @@
       <c r="BU32" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BV32" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="33" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -9411,8 +9481,11 @@
       <c r="BU33" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="BV33" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="34" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -9631,6 +9704,9 @@
         <v>31</v>
       </c>
       <c r="BU34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BV34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9644,7 +9720,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BS4:BT30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 BT31:BT34 H33:I33 BV4:DH30">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BS4:BT30 BV4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 BT31:BT34 H33:I33 BV31:BV34">
     <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9664,7 +9740,7 @@
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:BR3 BS3:BS34 BN4:BR34 G31:I32 BT3:DH3 BU4:BU34">
+  <conditionalFormatting sqref="BF3:BR3 BT3:DH3 BS3:BS34 BN4:BR34 BU4:BU34 G31:I32">
     <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4912965D-9497-476E-BF15-F8FE769ABD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1789B0-0ABF-4552-AF90-FAA8BD92A20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="57">
   <si>
     <t>Aluno</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>REMOTO</t>
+  </si>
+  <si>
+    <t>5/P</t>
   </si>
 </sst>
 </file>
@@ -658,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DT34"/>
+  <dimension ref="A1:DS34"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -688,10 +691,10 @@
     <col min="66" max="68" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="69" max="70" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="72" max="107" width="7.7109375" customWidth="1"/>
+    <col min="72" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -903,11 +906,9 @@
         <v>33</v>
       </c>
       <c r="BV1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="BW1" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="BW1" s="2"/>
       <c r="BX1" s="2"/>
       <c r="BY1" s="2"/>
       <c r="BZ1" s="2"/>
@@ -918,15 +919,14 @@
       <c r="CE1" s="2"/>
       <c r="CF1" s="2"/>
       <c r="CG1" s="2"/>
-      <c r="CH1" s="2"/>
-      <c r="CI1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="2"/>
       <c r="CJ1" s="2"/>
       <c r="CK1" s="2"/>
       <c r="CL1" s="2"/>
       <c r="CM1" s="2"/>
-      <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1147,11 +1147,9 @@
         <v>46322</v>
       </c>
       <c r="BV2" s="2">
-        <v>46322</v>
-      </c>
-      <c r="BW2" s="2">
         <v>46324</v>
       </c>
+      <c r="BW2" s="3"/>
       <c r="BX2" s="3"/>
       <c r="BY2" s="3"/>
       <c r="BZ2" s="3"/>
@@ -1168,9 +1166,8 @@
       <c r="CK2" s="3"/>
       <c r="CL2" s="3"/>
       <c r="CM2" s="3"/>
-      <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1443,9 +1440,8 @@
       <c r="DQ3" s="3"/>
       <c r="DR3" s="3"/>
       <c r="DS3" s="3"/>
-      <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1718,9 +1714,8 @@
       <c r="DQ4" s="3"/>
       <c r="DR4" s="3"/>
       <c r="DS4" s="3"/>
-      <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1993,9 +1988,8 @@
       <c r="DQ5" s="3"/>
       <c r="DR5" s="3"/>
       <c r="DS5" s="3"/>
-      <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -2231,8 +2225,8 @@
       <c r="CF6" s="3"/>
       <c r="CG6" s="3"/>
       <c r="CH6" s="3"/>
-      <c r="CI6" s="3"/>
-      <c r="CJ6" s="5"/>
+      <c r="CI6" s="5"/>
+      <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
       <c r="CM6" s="3"/>
@@ -2268,9 +2262,8 @@
       <c r="DQ6" s="3"/>
       <c r="DR6" s="3"/>
       <c r="DS6" s="3"/>
-      <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2506,8 +2499,8 @@
       <c r="CF7" s="3"/>
       <c r="CG7" s="3"/>
       <c r="CH7" s="3"/>
-      <c r="CI7" s="3"/>
-      <c r="CJ7" s="4"/>
+      <c r="CI7" s="4"/>
+      <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
       <c r="CM7" s="3"/>
@@ -2543,9 +2536,8 @@
       <c r="DQ7" s="3"/>
       <c r="DR7" s="3"/>
       <c r="DS7" s="3"/>
-      <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2818,9 +2810,8 @@
       <c r="DQ8" s="3"/>
       <c r="DR8" s="3"/>
       <c r="DS8" s="3"/>
-      <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -3039,10 +3030,10 @@
         <v>31</v>
       </c>
       <c r="BU9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="BV9" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="BV9" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="BW9" s="3"/>
       <c r="BX9" s="3"/>
@@ -3093,9 +3084,8 @@
       <c r="DQ9" s="3"/>
       <c r="DR9" s="3"/>
       <c r="DS9" s="3"/>
-      <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -3368,9 +3358,8 @@
       <c r="DQ10" s="3"/>
       <c r="DR10" s="3"/>
       <c r="DS10" s="3"/>
-      <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3634,9 +3623,8 @@
       <c r="DQ11" s="3"/>
       <c r="DR11" s="3"/>
       <c r="DS11" s="3"/>
-      <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3909,9 +3897,8 @@
       <c r="DQ12" s="3"/>
       <c r="DR12" s="3"/>
       <c r="DS12" s="3"/>
-      <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -4184,9 +4171,8 @@
       <c r="DQ13" s="3"/>
       <c r="DR13" s="3"/>
       <c r="DS13" s="3"/>
-      <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -4459,9 +4445,8 @@
       <c r="DQ14" s="3"/>
       <c r="DR14" s="3"/>
       <c r="DS14" s="3"/>
-      <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4734,9 +4719,8 @@
       <c r="DQ15" s="3"/>
       <c r="DR15" s="3"/>
       <c r="DS15" s="3"/>
-      <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -5009,9 +4993,8 @@
       <c r="DQ16" s="3"/>
       <c r="DR16" s="3"/>
       <c r="DS16" s="3"/>
-      <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -5263,9 +5246,8 @@
       <c r="DQ17" s="3"/>
       <c r="DR17" s="3"/>
       <c r="DS17" s="3"/>
-      <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -5538,9 +5520,8 @@
       <c r="DQ18" s="3"/>
       <c r="DR18" s="3"/>
       <c r="DS18" s="3"/>
-      <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -5813,9 +5794,8 @@
       <c r="DQ19" s="3"/>
       <c r="DR19" s="3"/>
       <c r="DS19" s="3"/>
-      <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -6067,9 +6047,8 @@
       <c r="DQ20" s="3"/>
       <c r="DR20" s="3"/>
       <c r="DS20" s="3"/>
-      <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -6342,9 +6321,8 @@
       <c r="DQ21" s="3"/>
       <c r="DR21" s="3"/>
       <c r="DS21" s="3"/>
-      <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -6617,9 +6595,8 @@
       <c r="DQ22" s="3"/>
       <c r="DR22" s="3"/>
       <c r="DS22" s="3"/>
-      <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -6892,9 +6869,8 @@
       <c r="DQ23" s="3"/>
       <c r="DR23" s="3"/>
       <c r="DS23" s="3"/>
-      <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -7167,9 +7143,8 @@
       <c r="DQ24" s="3"/>
       <c r="DR24" s="3"/>
       <c r="DS24" s="3"/>
-      <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -7442,9 +7417,8 @@
       <c r="DQ25" s="3"/>
       <c r="DR25" s="3"/>
       <c r="DS25" s="3"/>
-      <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -7717,9 +7691,8 @@
       <c r="DQ26" s="3"/>
       <c r="DR26" s="3"/>
       <c r="DS26" s="3"/>
-      <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -7992,9 +7965,8 @@
       <c r="DQ27" s="3"/>
       <c r="DR27" s="3"/>
       <c r="DS27" s="3"/>
-      <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -8267,9 +8239,8 @@
       <c r="DQ28" s="3"/>
       <c r="DR28" s="3"/>
       <c r="DS28" s="3"/>
-      <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -8482,7 +8453,7 @@
         <v>32</v>
       </c>
       <c r="BV29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BW29" s="3"/>
       <c r="BX29" s="3"/>
@@ -8533,9 +8504,8 @@
       <c r="DQ29" s="3"/>
       <c r="DR29" s="3"/>
       <c r="DS29" s="3"/>
-      <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -8808,9 +8778,8 @@
       <c r="DQ30" s="3"/>
       <c r="DR30" s="3"/>
       <c r="DS30" s="3"/>
-      <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -9035,7 +9004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -9715,12 +9684,12 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="U3:AS34">
+  <conditionalFormatting sqref="U3:AS34 BT3:DG3">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BS4:BT30 BV4:DH30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 BT31:BT34 H33:I33 BV31:BV34">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BS4:DG30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BT31:BV34">
     <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9740,7 +9709,7 @@
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:BR3 BT3:DH3 BS3:BS34 BN4:BR34 BU4:BU34 G31:I32">
+  <conditionalFormatting sqref="BF3:BR3 BS3:BS34 BN4:BR34 G31:I32">
     <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1789B0-0ABF-4552-AF90-FAA8BD92A20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32606DC-691D-4562-9A8D-4586F3E4E842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="58">
   <si>
     <t>Aluno</t>
   </si>
@@ -210,12 +210,15 @@
   <si>
     <t>5/P</t>
   </si>
+  <si>
+    <t>F | 5P</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,6 +259,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -278,7 +288,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -289,12 +299,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3033,7 +3064,7 @@
         <v>56</v>
       </c>
       <c r="BV9" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="BW9" s="3"/>
       <c r="BX9" s="3"/>
@@ -4398,7 +4429,7 @@
       </c>
       <c r="BW14" s="3"/>
       <c r="BX14" s="3"/>
-      <c r="BY14" s="3"/>
+      <c r="BY14" s="8"/>
       <c r="BZ14" s="3"/>
       <c r="CA14" s="3"/>
       <c r="CB14" s="3"/>
@@ -6544,7 +6575,7 @@
         <v>31</v>
       </c>
       <c r="BV22" s="3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="BW22" s="3"/>
       <c r="BX22" s="3"/>
@@ -9226,7 +9257,7 @@
         <v>31</v>
       </c>
       <c r="BV32" s="3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:74" x14ac:dyDescent="0.25">
@@ -9684,44 +9715,54 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="U3:AS34 BT3:DG3">
+  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BT31:BV34 BS4:DG30">
+    <cfRule type="cellIs" dxfId="10" priority="16" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB9">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB32">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 BH4:BH30 BJ4:BM30 BS4:DG30 BG4:BG34 BI4:BI34 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 BK31:BM34 H33:I33 BT31:BV34">
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF3:BR3 BS3:BS34 BN4:BR34 G31:I32">
+    <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BH3:BI34">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BJ16">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BJ16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BT3:DG3 U3:AS34">
     <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH3:BI34">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
+  <conditionalFormatting sqref="BV32">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BV32)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ16">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BJ16)))</formula>
+  <conditionalFormatting sqref="BV22">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BV22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -10106,7 +10147,7 @@
     <sortCondition ref="B1:B33"/>
   </sortState>
   <conditionalFormatting sqref="C2:C33">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
